--- a/franquias/pwr_reports/Keys Summary - Franquias (Stores)(2026-08-31 - 2026-09-06).xlsx
+++ b/franquias/pwr_reports/Keys Summary - Franquias (Stores)(2026-08-31 - 2026-09-06).xlsx
@@ -852,48 +852,48 @@
   </si>
   <si>
     <t>174
-150</t>
-  </si>
-  <si>
-    <t>183</t>
-  </si>
-  <si>
-    <t>R$ 6.460.349,58</t>
-  </si>
-  <si>
-    <t>R$ 43.693,19
-R$ 41.885,82</t>
-  </si>
-  <si>
-    <t>9.2%
-8.6%</t>
-  </si>
-  <si>
-    <t>466.6</t>
-  </si>
-  <si>
-    <t>(8.8%)</t>
-  </si>
-  <si>
-    <t>16.6%</t>
-  </si>
-  <si>
-    <t>(24.8%)</t>
+148</t>
+  </si>
+  <si>
+    <t>152</t>
+  </si>
+  <si>
+    <t>R$ 6.731.823,03</t>
+  </si>
+  <si>
+    <t>R$ 44.205,22
+R$ 43.840,44</t>
+  </si>
+  <si>
+    <t>(1.4%)
+(0.9%)</t>
+  </si>
+  <si>
+    <t>472.0</t>
+  </si>
+  <si>
+    <t>(8.9%)</t>
+  </si>
+  <si>
+    <t>14.8%</t>
+  </si>
+  <si>
+    <t>(27.6%)</t>
   </si>
   <si>
     <t>3.1%</t>
   </si>
   <si>
-    <t>0.5%</t>
-  </si>
-  <si>
-    <t>30.5</t>
-  </si>
-  <si>
-    <t>61.7%</t>
-  </si>
-  <si>
-    <t>17.6%</t>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>30.6</t>
+  </si>
+  <si>
+    <t>61.5%</t>
+  </si>
+  <si>
+    <t>17.8%</t>
   </si>
   <si>
     <t>6.2</t>
@@ -902,16 +902,16 @@
     <t>8.8</t>
   </si>
   <si>
-    <t>14.5</t>
+    <t>15.2</t>
   </si>
   <si>
     <t>21.8</t>
   </si>
   <si>
-    <t>59.6%</t>
-  </si>
-  <si>
-    <t>-R$ 238.926,77</t>
+    <t>59.4%</t>
+  </si>
+  <si>
+    <t>-R$ 248.044,03</t>
   </si>
   <si>
     <t>2.78</t>
@@ -1567,7 +1567,7 @@
         <v>61977.470000000008</v>
       </c>
       <c r="Q2" s="6">
-        <v>0.22399366451764524</v>
+        <v>0.08736676669398924</v>
       </c>
       <c r="R2" s="7">
         <v>600</v>
@@ -1603,7 +1603,7 @@
         <v>10.095384615384615</v>
       </c>
       <c r="AC2" s="8">
-        <v>18.444424999999999</v>
+        <v>19.166475999999999</v>
       </c>
       <c r="AD2" s="8">
         <v>24.51746579520697</v>
@@ -1696,7 +1696,7 @@
         <v>79043.279999999999</v>
       </c>
       <c r="Q3" s="6">
-        <v>0.29980980546088221</v>
+        <v>0.23845855911075353</v>
       </c>
       <c r="R3" s="7">
         <v>729</v>
@@ -1732,7 +1732,7 @@
         <v>5.0628477797513325</v>
       </c>
       <c r="AC3" s="8">
-        <v>9.3240739999999995</v>
+        <v>9.9420500000000001</v>
       </c>
       <c r="AD3" s="8">
         <v>15.745789298245613</v>
@@ -1827,7 +1827,7 @@
         <v>75922.360000000001</v>
       </c>
       <c r="Q4" s="6">
-        <v>0.37820567628094981</v>
+        <v>0.31315418929345618</v>
       </c>
       <c r="R4" s="7">
         <v>850</v>
@@ -1863,7 +1863,7 @@
         <v>8.3012530827067668</v>
       </c>
       <c r="AC4" s="8">
-        <v>12.467615</v>
+        <v>12.151592000000001</v>
       </c>
       <c r="AD4" s="8">
         <v>18.553435123367201</v>
@@ -1958,7 +1958,7 @@
         <v>24251.739999999998</v>
       </c>
       <c r="Q5" s="6">
-        <v>0.11153868541678791</v>
+        <v>0.0094183420421503072</v>
       </c>
       <c r="R5" s="7">
         <v>258</v>
@@ -1994,7 +1994,7 @@
         <v>14.239173722627738</v>
       </c>
       <c r="AC5" s="8">
-        <v>20.226127000000002</v>
+        <v>20.213909000000001</v>
       </c>
       <c r="AD5" s="8">
         <v>26.635888321167883</v>
@@ -2089,7 +2089,7 @@
         <v>75480.659999999989</v>
       </c>
       <c r="Q6" s="6">
-        <v>0.22941881639341033</v>
+        <v>0.087836400520911795</v>
       </c>
       <c r="R6" s="7">
         <v>780</v>
@@ -2220,7 +2220,7 @@
         <v>72580.089999999997</v>
       </c>
       <c r="Q7" s="6">
-        <v>0.13391065113855705</v>
+        <v>0.0052387861583582662</v>
       </c>
       <c r="R7" s="7">
         <v>722</v>
@@ -2256,7 +2256,7 @@
         <v>8.6473576576576576</v>
       </c>
       <c r="AC7" s="8">
-        <v>14.456253</v>
+        <v>15.292256</v>
       </c>
       <c r="AD7" s="8">
         <v>22.076636964285715</v>
@@ -2351,7 +2351,7 @@
         <v>42770.029999999992</v>
       </c>
       <c r="Q8" s="6">
-        <v>0.078383852442296842</v>
+        <v>-0.032686882750288415</v>
       </c>
       <c r="R8" s="7">
         <v>487</v>
@@ -2387,7 +2387,7 @@
         <v>11.031119531250001</v>
       </c>
       <c r="AC8" s="8">
-        <v>15.690597</v>
+        <v>16.529851000000001</v>
       </c>
       <c r="AD8" s="8">
         <v>23.187612260536397</v>
@@ -2482,7 +2482,7 @@
         <v>98312.700000000026</v>
       </c>
       <c r="Q9" s="6">
-        <v>0.48464407349413019</v>
+        <v>0.41456878060066682</v>
       </c>
       <c r="R9" s="7">
         <v>937</v>
@@ -2518,7 +2518,7 @@
         <v>4.7213311320754716</v>
       </c>
       <c r="AC9" s="8">
-        <v>15.577544</v>
+        <v>16.527726999999999</v>
       </c>
       <c r="AD9" s="8">
         <v>23.326909133126936</v>
@@ -2613,7 +2613,7 @@
         <v>64352.07</v>
       </c>
       <c r="Q10" s="6">
-        <v>0.15092619303925781</v>
+        <v>0.023942457398760775</v>
       </c>
       <c r="R10" s="7">
         <v>633</v>
@@ -2649,7 +2649,7 @@
         <v>7.4884740667976422</v>
       </c>
       <c r="AC10" s="8">
-        <v>14.995343</v>
+        <v>14.552481</v>
       </c>
       <c r="AD10" s="8">
         <v>21.408999220272904</v>
@@ -2744,7 +2744,7 @@
         <v>121794.91</v>
       </c>
       <c r="Q11" s="6">
-        <v>0.28914251081686571</v>
+        <v>0.22829478128379699</v>
       </c>
       <c r="R11" s="7">
         <v>1279</v>
@@ -2780,7 +2780,7 @@
         <v>7.00328798185941</v>
       </c>
       <c r="AC11" s="8">
-        <v>20.575167</v>
+        <v>20.650039</v>
       </c>
       <c r="AD11" s="8">
         <v>27.422683071748878</v>
@@ -2875,7 +2875,7 @@
         <v>30173.919999999998</v>
       </c>
       <c r="Q12" s="6">
-        <v>-0.34274556819310542</v>
+        <v>-0.12126407374714865</v>
       </c>
       <c r="R12" s="7">
         <v>353.5</v>
@@ -3004,7 +3004,7 @@
         <v>71782</v>
       </c>
       <c r="Q13" s="6">
-        <v>0.39767413876426305</v>
+        <v>0.24568067315554853</v>
       </c>
       <c r="R13" s="7">
         <v>692</v>
@@ -3040,7 +3040,7 @@
         <v>8.3840836492890993</v>
       </c>
       <c r="AC13" s="8">
-        <v>14.565337</v>
+        <v>14.919841</v>
       </c>
       <c r="AD13" s="8">
         <v>21.744784235294116</v>
@@ -3135,7 +3135,7 @@
         <v>110428.35000000002</v>
       </c>
       <c r="Q14" s="6">
-        <v>0.078997306032850823</v>
+        <v>-0.044358010663403391</v>
       </c>
       <c r="R14" s="7">
         <v>968.99999999999989</v>
@@ -3171,7 +3171,7 @@
         <v>9.6733878688524584</v>
       </c>
       <c r="AC14" s="8">
-        <v>14.437550999999999</v>
+        <v>13.475073</v>
       </c>
       <c r="AD14" s="8">
         <v>18.471993225331367</v>
@@ -3266,7 +3266,7 @@
         <v>34308.099999999999</v>
       </c>
       <c r="Q15" s="6">
-        <v>-0.37456806620356742</v>
+        <v>-0.44665407980944882</v>
       </c>
       <c r="R15" s="7">
         <v>346</v>
@@ -3302,7 +3302,7 @@
         <v>6.5195610526315786</v>
       </c>
       <c r="AC15" s="8">
-        <v>10.499499</v>
+        <v>9.5800479999999997</v>
       </c>
       <c r="AD15" s="8">
         <v>16.841501485148513</v>
@@ -3354,7 +3354,7 @@
         <v>19546</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C16" s="4">
         <v>44</v>
@@ -3391,59 +3391,59 @@
         <v>52</v>
       </c>
       <c r="O16" s="5">
-        <v>39514.860000000001</v>
+        <v>45298.690000000002</v>
       </c>
       <c r="P16" s="5">
-        <v>46100.670000000006</v>
+        <v>45298.690000000002</v>
       </c>
       <c r="Q16" s="6">
-        <v>0.1500045650276971</v>
+        <v>-0.037444696623755713</v>
       </c>
       <c r="R16" s="7">
-        <v>486.5</v>
+        <v>484</v>
       </c>
       <c r="S16" s="6">
-        <v>0.024570024570024662</v>
+        <v>-0.060194174757281504</v>
       </c>
       <c r="T16" s="6">
-        <v>0.00065267344993756777</v>
+        <v>0.00066418697759250867</v>
       </c>
       <c r="U16" s="6">
-        <v>-0.31724520091935032</v>
+        <v>-0.31526879033367189</v>
       </c>
       <c r="V16" s="6">
-        <v>0.060936809595175084</v>
+        <v>0.062596147923924497</v>
       </c>
       <c r="W16" s="6">
-        <v>0.05246430077191213</v>
+        <v>0.053999431330133386</v>
       </c>
       <c r="X16" s="8">
-        <v>27.982638888888889</v>
+        <v>27.52707509881423</v>
       </c>
       <c r="Y16" s="6">
-        <v>0.55760368663594473</v>
+        <v>0.53937007874015752</v>
       </c>
       <c r="Z16" s="6">
-        <v>0.087962962962962965</v>
+        <v>0.083003952569169967</v>
       </c>
       <c r="AA16" s="8">
-        <v>3.1423324455205814</v>
+        <v>3.0726041666666664</v>
       </c>
       <c r="AB16" s="8">
-        <v>10.0102625</v>
+        <v>9.7142198412698413</v>
       </c>
       <c r="AC16" s="8">
-        <v>13.044138</v>
+        <v>13.126699</v>
       </c>
       <c r="AD16" s="8">
-        <v>20.07330277777778</v>
+        <v>19.698155731225295</v>
       </c>
       <c r="AE16" s="6">
-        <v>0.60185185185185186</v>
+        <v>0.62055335968379444</v>
       </c>
       <c r="AF16" s="9"/>
       <c r="AG16" s="5">
-        <v>-6312.9099999999999</v>
+        <v>-7478.6499999999996</v>
       </c>
       <c r="AH16" s="10">
         <v>2</v>
@@ -3485,7 +3485,7 @@
         <v>19547</v>
       </c>
       <c r="B17" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C17" s="4">
         <v>44</v>
@@ -3522,55 +3522,55 @@
         <v>52</v>
       </c>
       <c r="O17" s="5">
-        <v>30930.509999999995</v>
+        <v>37020.869999999995</v>
       </c>
       <c r="P17" s="5">
-        <v>36085.594999999994</v>
+        <v>37020.869999999995</v>
       </c>
       <c r="Q17" s="6">
-        <v>-0.043438723432568382</v>
+        <v>-0.1178809338805108</v>
       </c>
       <c r="R17" s="7">
-        <v>401.33333333333337</v>
+        <v>411</v>
       </c>
       <c r="S17" s="6">
-        <v>-0.19626168224299056</v>
+        <v>-0.24725274725274726</v>
       </c>
       <c r="T17" s="6">
-        <v>0.33000846090154995</v>
+        <v>0.27571826377932229</v>
       </c>
       <c r="U17" s="6">
-        <v>-3.6921256713840154</v>
+        <v>-3.7262341484681474</v>
       </c>
       <c r="V17" s="6">
-        <v>0.033562734659079337</v>
+        <v>0.033169722915749954</v>
       </c>
       <c r="W17" s="6">
-        <v>0.0079973624747862234</v>
+        <v>0.0082148798772152028</v>
       </c>
       <c r="X17" s="8">
-        <v>37.101247593582883</v>
+        <v>35.786988157894733</v>
       </c>
       <c r="Y17" s="6">
-        <v>0.34920634920634919</v>
+        <v>0.32608695652173914</v>
       </c>
       <c r="Z17" s="6">
-        <v>0.35828877005347592</v>
+        <v>0.31578947368421051</v>
       </c>
       <c r="AA17" s="8">
-        <v>9.3126684971098275</v>
+        <v>8.9311243373493969</v>
       </c>
       <c r="AB17" s="8">
-        <v>10.687362087912087</v>
+        <v>10.025784304932735</v>
       </c>
       <c r="AC17" s="8">
-        <v>20.855119999999999</v>
+        <v>20.322737</v>
       </c>
       <c r="AD17" s="8">
-        <v>27.737234042553194</v>
+        <v>26.816084279475984</v>
       </c>
       <c r="AE17" s="6">
-        <v>0.33155080213903743</v>
+        <v>0.38157894736842107</v>
       </c>
       <c r="AF17" s="9"/>
       <c r="AG17" s="5">
@@ -3691,7 +3691,7 @@
         <v>11.854849090909092</v>
       </c>
       <c r="AC18" s="8">
-        <v>9.295166</v>
+        <v>15.898992</v>
       </c>
       <c r="AD18" s="8">
         <v>22.711109909909908</v>
@@ -3788,7 +3788,7 @@
         <v>57037.189999999995</v>
       </c>
       <c r="Q19" s="6">
-        <v>0.027793414878510836</v>
+        <v>-0.11322018456314542</v>
       </c>
       <c r="R19" s="7">
         <v>546</v>
@@ -3824,7 +3824,7 @@
         <v>5.0171557184750739</v>
       </c>
       <c r="AC19" s="8">
-        <v>9.6131469999999997</v>
+        <v>11.319925</v>
       </c>
       <c r="AD19" s="8">
         <v>18.643333698630137</v>
@@ -3919,7 +3919,7 @@
         <v>94548.709999999992</v>
       </c>
       <c r="Q20" s="6">
-        <v>0.22246487967574957</v>
+        <v>0.030659682430397295</v>
       </c>
       <c r="R20" s="7">
         <v>922</v>
@@ -3955,7 +3955,7 @@
         <v>6.4778410841654779</v>
       </c>
       <c r="AC20" s="8">
-        <v>9.4477949999999993</v>
+        <v>9.3008539999999993</v>
       </c>
       <c r="AD20" s="8">
         <v>15.245708961593172</v>
@@ -4007,7 +4007,7 @@
         <v>19553</v>
       </c>
       <c r="B21" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C21" s="4">
         <v>44</v>
@@ -4042,55 +4042,55 @@
         <v>52</v>
       </c>
       <c r="O21" s="5">
-        <v>42733.800000000003</v>
+        <v>55585.120000000003</v>
       </c>
       <c r="P21" s="5">
-        <v>49856.100000000006</v>
+        <v>55585.120000000003</v>
       </c>
       <c r="Q21" s="6">
-        <v>0.16872714111104803</v>
+        <v>0.15927075697078208</v>
       </c>
       <c r="R21" s="7">
-        <v>448</v>
+        <v>508</v>
       </c>
       <c r="S21" s="6">
-        <v>0.049180327868852514</v>
+        <v>0.069473684210526354</v>
       </c>
       <c r="T21" s="6">
-        <v>0.32425854475848159</v>
+        <v>0.3026868881456044</v>
       </c>
       <c r="U21" s="6">
-        <v>-0.028557493131900275</v>
+        <v>-0.049343655280405976</v>
       </c>
       <c r="V21" s="6">
-        <v>0.02559264563413504</v>
+        <v>0.022609405178939973</v>
       </c>
       <c r="W21" s="6">
-        <v>-0.0035075045982337167</v>
+        <v>-0.0036391663812185707</v>
       </c>
       <c r="X21" s="8">
-        <v>33.093233082706767</v>
+        <v>31.632388059701494</v>
       </c>
       <c r="Y21" s="6">
-        <v>0.75939849624060152</v>
+        <v>0.74328358208955225</v>
       </c>
       <c r="Z21" s="6">
-        <v>0.12781954887218044</v>
+        <v>0.10149253731343283</v>
       </c>
       <c r="AA21" s="8">
-        <v>7.727750125944584</v>
+        <v>6.546264559386973</v>
       </c>
       <c r="AB21" s="8">
-        <v>9.8648359848484848</v>
+        <v>9.4321212121212117</v>
       </c>
       <c r="AC21" s="8">
         <v>17.567685000000001</v>
       </c>
       <c r="AD21" s="8">
-        <v>24.287845112781952</v>
+        <v>22.792637313432834</v>
       </c>
       <c r="AE21" s="6">
-        <v>0.68796992481203012</v>
+        <v>0.70447761194029845</v>
       </c>
       <c r="AF21" s="9"/>
       <c r="AG21" s="5">
@@ -4179,7 +4179,7 @@
         <v>61082.929999999993</v>
       </c>
       <c r="Q22" s="6">
-        <v>0.15963593582668412</v>
+        <v>0.029399506997238367</v>
       </c>
       <c r="R22" s="7">
         <v>651</v>
@@ -4215,7 +4215,7 @@
         <v>12.675487531806615</v>
       </c>
       <c r="AC22" s="8">
-        <v>21.138476000000001</v>
+        <v>20.344242000000001</v>
       </c>
       <c r="AD22" s="8">
         <v>26.945107960199003</v>
@@ -4310,7 +4310,7 @@
         <v>29944.310000000001</v>
       </c>
       <c r="Q23" s="6">
-        <v>0.0026301021638157618</v>
+        <v>-0.089707453292662831</v>
       </c>
       <c r="R23" s="7">
         <v>337</v>
@@ -4346,7 +4346,7 @@
         <v>4.7155092592592593</v>
       </c>
       <c r="AC23" s="8">
-        <v>8.9466959999999993</v>
+        <v>8.2679419999999997</v>
       </c>
       <c r="AD23" s="8">
         <v>15.914148444444445</v>
@@ -4398,7 +4398,7 @@
         <v>19565</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>44</v>
@@ -4435,55 +4435,55 @@
         <v>52</v>
       </c>
       <c r="O24" s="5">
-        <v>40013.540000000001</v>
+        <v>52412.449999999997</v>
       </c>
       <c r="P24" s="5">
-        <v>46682.46333333334</v>
+        <v>52412.449999999997</v>
       </c>
       <c r="Q24" s="6">
-        <v>-0.02096399478182609</v>
+        <v>-0.020803359565459645</v>
       </c>
       <c r="R24" s="7">
-        <v>527.33333333333326</v>
+        <v>592</v>
       </c>
       <c r="S24" s="6">
-        <v>-0.12741312741312738</v>
+        <v>-0.13828238719068409</v>
       </c>
       <c r="T24" s="6">
-        <v>0.28952959923066041</v>
+        <v>0.28386752384214059</v>
       </c>
       <c r="U24" s="6">
-        <v>-0.036064937018819132</v>
+        <v>-0.037776474864273664</v>
       </c>
       <c r="V24" s="6">
-        <v>0.096567399435291149</v>
+        <v>0.082629546987404712</v>
       </c>
       <c r="W24" s="6">
-        <v>0.061469030233266039</v>
+        <v>0.051523197255613884</v>
       </c>
       <c r="X24" s="8">
-        <v>23.616023166023165</v>
+        <v>23.46881081871345</v>
       </c>
       <c r="Y24" s="6">
-        <v>0.99227799227799229</v>
+        <v>0.98830409356725146</v>
       </c>
       <c r="Z24" s="6">
-        <v>0.042471042471042469</v>
+        <v>0.032163742690058478</v>
       </c>
       <c r="AA24" s="8">
-        <v>2.728625512528474</v>
+        <v>2.7664343205574911</v>
       </c>
       <c r="AB24" s="8">
-        <v>6.0784757847533628</v>
+        <v>5.4333884868421052</v>
       </c>
       <c r="AC24" s="8">
-        <v>8.8918839999999992</v>
+        <v>8.9023210000000006</v>
       </c>
       <c r="AD24" s="8">
-        <v>15.419369884169884</v>
+        <v>15.196491520467836</v>
       </c>
       <c r="AE24" s="6">
-        <v>0.82239382239382242</v>
+        <v>0.84210526315789469</v>
       </c>
       <c r="AF24" s="9"/>
       <c r="AG24" s="5">
@@ -4572,7 +4572,7 @@
         <v>115458.09</v>
       </c>
       <c r="Q25" s="6">
-        <v>0.44557482269317084</v>
+        <v>0.1528450611913641</v>
       </c>
       <c r="R25" s="7">
         <v>1271</v>
@@ -4608,7 +4608,7 @@
         <v>10.36922313559322</v>
       </c>
       <c r="AC25" s="8">
-        <v>14.836838</v>
+        <v>14.953181000000001</v>
       </c>
       <c r="AD25" s="8">
         <v>21.658940000000001</v>
@@ -4703,7 +4703,7 @@
         <v>49207.759999999995</v>
       </c>
       <c r="Q26" s="6">
-        <v>0.22431301244472168</v>
+        <v>-0.0099050222092376128</v>
       </c>
       <c r="R26" s="7">
         <v>572</v>
@@ -4739,7 +4739,7 @@
         <v>10.192058895705522</v>
       </c>
       <c r="AC26" s="8">
-        <v>13.355570999999999</v>
+        <v>13.52477</v>
       </c>
       <c r="AD26" s="8">
         <v>18.931525443786981</v>
@@ -4791,7 +4791,7 @@
         <v>19579</v>
       </c>
       <c r="B27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C27" s="4">
         <v>44</v>
@@ -4828,59 +4828,59 @@
         <v>52</v>
       </c>
       <c r="O27" s="5">
-        <v>28177.470000000001</v>
+        <v>34614.949999999997</v>
       </c>
       <c r="P27" s="5">
-        <v>32873.715000000004</v>
+        <v>34614.949999999997</v>
       </c>
       <c r="Q27" s="6">
-        <v>-0.15267641000156718</v>
+        <v>-0.24097528950535829</v>
       </c>
       <c r="R27" s="7">
-        <v>393.16666666666663</v>
+        <v>403</v>
       </c>
       <c r="S27" s="6">
-        <v>-0.10610079575596831</v>
+        <v>-0.098434004474272974</v>
       </c>
       <c r="T27" s="6">
-        <v>0.37701993472089579</v>
+        <v>0.33980682046341248</v>
       </c>
       <c r="U27" s="6">
-        <v>0.034451208713912211</v>
+        <v>0.0048203478554786306</v>
       </c>
       <c r="V27" s="6">
-        <v>0.052967441718507723</v>
+        <v>0.049925639066357171</v>
       </c>
       <c r="W27" s="6">
-        <v>0.0073654057656702323</v>
+        <v>0.0077747765055272361</v>
       </c>
       <c r="X27" s="8">
-        <v>31.817</v>
+        <v>31.232615894039736</v>
       </c>
       <c r="Y27" s="6">
-        <v>0.50996015936254979</v>
+        <v>0.56765676567656764</v>
       </c>
       <c r="Z27" s="6">
-        <v>0.26400000000000001</v>
+        <v>0.2185430463576159</v>
       </c>
       <c r="AA27" s="8">
-        <v>6.2348097142857144</v>
+        <v>6.6806492788461531</v>
       </c>
       <c r="AB27" s="8">
-        <v>10.696448360655737</v>
+        <v>9.7430182432432435</v>
       </c>
       <c r="AC27" s="8">
-        <v>12.01821</v>
+        <v>17.195004000000001</v>
       </c>
       <c r="AD27" s="8">
-        <v>23.838999999999999</v>
+        <v>23.517549668874175</v>
       </c>
       <c r="AE27" s="6">
-        <v>0.58399999999999996</v>
+        <v>0.60596026490066224</v>
       </c>
       <c r="AF27" s="9"/>
       <c r="AG27" s="5">
-        <v>-272.19999999999999</v>
+        <v>-284.02999999999997</v>
       </c>
       <c r="AH27" s="10">
         <v>3</v>
@@ -4965,7 +4965,7 @@
         <v>44062.760000000002</v>
       </c>
       <c r="Q28" s="6">
-        <v>-0.15209526727146483</v>
+        <v>-0.19381276330720243</v>
       </c>
       <c r="R28" s="7">
         <v>416</v>
@@ -5001,7 +5001,7 @@
         <v>8.7955285714285711</v>
       </c>
       <c r="AC28" s="8">
-        <v>17.261196999999999</v>
+        <v>19.88815</v>
       </c>
       <c r="AD28" s="8">
         <v>26.048759546925567</v>
@@ -5053,7 +5053,7 @@
         <v>19581</v>
       </c>
       <c r="B29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C29" s="4">
         <v>44</v>
@@ -5090,55 +5090,55 @@
         <v>52</v>
       </c>
       <c r="O29" s="5">
-        <v>38559.789999999994</v>
+        <v>56445.789999999994</v>
       </c>
       <c r="P29" s="5">
-        <v>44986.421666666662</v>
+        <v>56445.789999999994</v>
       </c>
       <c r="Q29" s="6">
-        <v>-0.12385971629675263</v>
+        <v>0.12367699312266334</v>
       </c>
       <c r="R29" s="7">
-        <v>444.5</v>
+        <v>555</v>
       </c>
       <c r="S29" s="6">
-        <v>-0.17710583153347748</v>
+        <v>-0.071906354515050119</v>
       </c>
       <c r="T29" s="6">
-        <v>0.3558109315429363</v>
+        <v>0.34407836084852389</v>
       </c>
       <c r="U29" s="6">
-        <v>0.037328906614895983</v>
+        <v>0.025415622670884756</v>
       </c>
       <c r="V29" s="6">
-        <v>0.043517923723132304</v>
+        <v>0.042636492464717034</v>
       </c>
       <c r="W29" s="6">
-        <v>0.019529981880088039</v>
+        <v>0.022360755337111942</v>
       </c>
       <c r="X29" s="8">
-        <v>44.069471947194714</v>
+        <v>47.07143409610984</v>
       </c>
       <c r="Y29" s="6">
-        <v>0.17377049180327869</v>
+        <v>0.12727272727272726</v>
       </c>
       <c r="Z29" s="6">
-        <v>0.50495049504950495</v>
+        <v>0.59038901601830662</v>
       </c>
       <c r="AA29" s="8">
-        <v>4.192057291666667</v>
+        <v>7.4566967567567568</v>
       </c>
       <c r="AB29" s="8">
-        <v>19.547627118644069</v>
+        <v>19.398352941176469</v>
       </c>
       <c r="AC29" s="8">
-        <v>23.978583</v>
+        <v>23.950869000000001</v>
       </c>
       <c r="AD29" s="8">
-        <v>31.145434653465344</v>
+        <v>34.100343249427915</v>
       </c>
       <c r="AE29" s="6">
-        <v>0.24422442244224424</v>
+        <v>0.18764302059496568</v>
       </c>
       <c r="AF29" s="9"/>
       <c r="AG29" s="5">
@@ -5227,7 +5227,7 @@
         <v>69471.169999999998</v>
       </c>
       <c r="Q30" s="6">
-        <v>0.14059187627241077</v>
+        <v>0.0064334162138373063</v>
       </c>
       <c r="R30" s="7">
         <v>698</v>
@@ -5263,7 +5263,7 @@
         <v>4.8449329145728646</v>
       </c>
       <c r="AC30" s="8">
-        <v>10.523509000000001</v>
+        <v>9.9720759999999995</v>
       </c>
       <c r="AD30" s="8">
         <v>16.206375250000001</v>
@@ -5315,7 +5315,7 @@
         <v>19596</v>
       </c>
       <c r="B31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C31" s="4">
         <v>44</v>
@@ -5350,59 +5350,57 @@
         <v>52</v>
       </c>
       <c r="O31" s="5">
-        <v>36583.25</v>
+        <v>49375.029999999999</v>
       </c>
       <c r="P31" s="5">
-        <v>42680.458333333336</v>
-      </c>
-      <c r="Q31" s="6">
-        <v>-0.031948128279255639</v>
-      </c>
+        <v>49375.029999999992</v>
+      </c>
+      <c r="Q31" s="6"/>
       <c r="R31" s="7">
-        <v>492.33333333333331</v>
+        <v>556</v>
       </c>
       <c r="S31" s="6">
-        <v>0.057644110275689275</v>
+        <v>0.051039697542533125</v>
       </c>
       <c r="T31" s="6">
-        <v>0.27715749420841507</v>
+        <v>0.28270829810128723</v>
       </c>
       <c r="U31" s="6">
-        <v>-0.073383805430080704</v>
+        <v>-0.071053917334328712</v>
       </c>
       <c r="V31" s="6">
-        <v>0.065947762978958949</v>
+        <v>0.057599357407985372</v>
       </c>
       <c r="W31" s="6">
-        <v>-0.0054543131077747324</v>
+        <v>-0.0075653624919316508</v>
       </c>
       <c r="X31" s="8">
-        <v>31.158797854077253</v>
+        <v>33.189384076433122</v>
       </c>
       <c r="Y31" s="6">
-        <v>0.88461538461538458</v>
+        <v>0.9015873015873016</v>
       </c>
       <c r="Z31" s="6">
-        <v>0.17167381974248927</v>
+        <v>0.23248407643312102</v>
       </c>
       <c r="AA31" s="8">
-        <v>5.234684520884521</v>
+        <v>6.3666972375690607</v>
       </c>
       <c r="AB31" s="8">
-        <v>9.6308589519650649</v>
+        <v>9.9670983818770225</v>
       </c>
       <c r="AC31" s="8">
-        <v>17.558764</v>
+        <v>16.202604999999998</v>
       </c>
       <c r="AD31" s="8">
-        <v>22.78075793991416</v>
+        <v>24.810774840764331</v>
       </c>
       <c r="AE31" s="6">
-        <v>0.58798283261802575</v>
+        <v>0.52229299363057324</v>
       </c>
       <c r="AF31" s="9"/>
       <c r="AG31" s="5">
-        <v>2196.54</v>
+        <v>2792.8400000000001</v>
       </c>
       <c r="AH31" s="10">
         <v>3</v>
@@ -5487,7 +5485,7 @@
         <v>66428.51999999999</v>
       </c>
       <c r="Q32" s="6">
-        <v>0.12159278841811005</v>
+        <v>-0.0056712280376127744</v>
       </c>
       <c r="R32" s="7">
         <v>758</v>
@@ -5523,7 +5521,7 @@
         <v>5.5726300458715601</v>
       </c>
       <c r="AC32" s="8">
-        <v>10.964812</v>
+        <v>12.478732000000001</v>
       </c>
       <c r="AD32" s="8">
         <v>19.175148660714285</v>
@@ -5616,7 +5614,7 @@
         <v>57370.749999999993</v>
       </c>
       <c r="Q33" s="6">
-        <v>0.24975574859434246</v>
+        <v>0.11694996627972709</v>
       </c>
       <c r="R33" s="7">
         <v>667</v>
@@ -5652,7 +5650,7 @@
         <v>13.745593678160919</v>
       </c>
       <c r="AC33" s="8">
-        <v>20.583957000000002</v>
+        <v>24.849029000000002</v>
       </c>
       <c r="AD33" s="8">
         <v>31.76537736389685</v>
@@ -5745,7 +5743,7 @@
         <v>50464.909999999996</v>
       </c>
       <c r="Q34" s="6">
-        <v>0.34559422096048387</v>
+        <v>0.28208189231712377</v>
       </c>
       <c r="R34" s="7">
         <v>588</v>
@@ -5781,7 +5779,7 @@
         <v>8.6479512500000002</v>
       </c>
       <c r="AC34" s="8">
-        <v>12.155405</v>
+        <v>12.266798</v>
       </c>
       <c r="AD34" s="8">
         <v>19.926755623721881</v>
@@ -5833,7 +5831,7 @@
         <v>19601</v>
       </c>
       <c r="B35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C35" s="4">
         <v>44</v>
@@ -5870,59 +5868,59 @@
         <v>52</v>
       </c>
       <c r="O35" s="5">
-        <v>33681.120000000003</v>
+        <v>44699.560000000005</v>
       </c>
       <c r="P35" s="5">
-        <v>39294.640000000007</v>
+        <v>44699.560000000005</v>
       </c>
       <c r="Q35" s="6">
-        <v>-0.18272294376346054</v>
+        <v>-0.1728889957996409</v>
       </c>
       <c r="R35" s="7">
-        <v>456.16666666666669</v>
+        <v>514</v>
       </c>
       <c r="S35" s="6">
-        <v>-0.19381443298969059</v>
+        <v>-0.23283582089552235</v>
       </c>
       <c r="T35" s="6">
-        <v>0.31816533416941001</v>
+        <v>0.31150975982761353</v>
       </c>
       <c r="U35" s="6">
-        <v>0.0097061736664338944</v>
+        <v>-0.0030570949691674822</v>
       </c>
       <c r="V35" s="6">
-        <v>0.066611086567192543</v>
+        <v>0.06445772620580606</v>
       </c>
       <c r="W35" s="6">
-        <v>0.025362755157785723</v>
+        <v>0.027625596314594599</v>
       </c>
       <c r="X35" s="8">
-        <v>23.077556175298803</v>
+        <v>22.767893558282211</v>
       </c>
       <c r="Y35" s="6">
-        <v>0.93625498007968122</v>
+        <v>0.93865030674846628</v>
       </c>
       <c r="Z35" s="6">
-        <v>0.019920318725099601</v>
+        <v>0.015337423312883436</v>
       </c>
       <c r="AA35" s="8">
-        <v>2.7795252688172045</v>
+        <v>2.9444557809330631</v>
       </c>
       <c r="AB35" s="8">
-        <v>5.3808745901639341</v>
+        <v>5.3978770700636938</v>
       </c>
       <c r="AC35" s="8">
-        <v>8.4617550000000001</v>
+        <v>8.2746429999999993</v>
       </c>
       <c r="AD35" s="8">
-        <v>15.925763745019921</v>
+        <v>15.970807975460122</v>
       </c>
       <c r="AE35" s="6">
-        <v>0.86852589641434264</v>
+        <v>0.88036809815950923</v>
       </c>
       <c r="AF35" s="9"/>
       <c r="AG35" s="5">
-        <v>-113.13</v>
+        <v>-166.53</v>
       </c>
       <c r="AH35" s="10">
         <v>4</v>
@@ -6102,7 +6100,7 @@
         <v>45733.149999999987</v>
       </c>
       <c r="Q37" s="6">
-        <v>-0.085399375762573171</v>
+        <v>-0.17946161461789012</v>
       </c>
       <c r="R37" s="7">
         <v>485.00000000000006</v>
@@ -6138,7 +6136,7 @@
         <v>12.185897435897436</v>
       </c>
       <c r="AC37" s="8">
-        <v>9.790476</v>
+        <v>19.893775000000002</v>
       </c>
       <c r="AD37" s="8">
         <v>27.233950205761317</v>
@@ -6231,7 +6229,7 @@
         <v>33755.010000000002</v>
       </c>
       <c r="Q38" s="6">
-        <v>0.27209527653507792</v>
+        <v>0.20314696531173793</v>
       </c>
       <c r="R38" s="7">
         <v>401</v>
@@ -6267,7 +6265,7 @@
         <v>2.9592595555555556</v>
       </c>
       <c r="AC38" s="8">
-        <v>6.2536259999999997</v>
+        <v>5.9832590000000003</v>
       </c>
       <c r="AD38" s="8">
         <v>12.920073777777777</v>
@@ -6319,7 +6317,7 @@
         <v>19609</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>44</v>
@@ -6356,59 +6354,59 @@
         <v>52</v>
       </c>
       <c r="O39" s="5">
-        <v>30108.419999999998</v>
+        <v>38970.830000000002</v>
       </c>
       <c r="P39" s="5">
-        <v>35126.489999999998</v>
+        <v>38970.830000000002</v>
       </c>
       <c r="Q39" s="6">
-        <v>-0.053455341020521963</v>
+        <v>-0.049300188111113918</v>
       </c>
       <c r="R39" s="7">
-        <v>375.66666666666663</v>
+        <v>420</v>
       </c>
       <c r="S39" s="6">
-        <v>-0.18066157760814261</v>
+        <v>-0.16500994035785288</v>
       </c>
       <c r="T39" s="6">
-        <v>0.33399348753604474</v>
+        <v>0.33432092926940482</v>
       </c>
       <c r="U39" s="6">
-        <v>-0.043269749790922275</v>
+        <v>-0.039713188043467379</v>
       </c>
       <c r="V39" s="6">
-        <v>0.017609459413678964</v>
+        <v>0.016443491195850844</v>
       </c>
       <c r="W39" s="6">
-        <v>-0.010296023504388475</v>
+        <v>-0.0090173470772883201</v>
       </c>
       <c r="X39" s="8">
-        <v>40.228307633587789</v>
+        <v>39.186280182926829</v>
       </c>
       <c r="Y39" s="6">
-        <v>0.35114503816793891</v>
+        <v>0.3597560975609756</v>
       </c>
       <c r="Z39" s="6">
-        <v>0.43129770992366412</v>
+        <v>0.40548780487804881</v>
       </c>
       <c r="AA39" s="8">
-        <v>5.8586914110429449</v>
+        <v>5.7410560283687939</v>
       </c>
       <c r="AB39" s="8">
-        <v>15.729566283524903</v>
+        <v>14.955351987767584</v>
       </c>
       <c r="AC39" s="8">
-        <v>19.733052000000001</v>
+        <v>21.898432</v>
       </c>
       <c r="AD39" s="8">
-        <v>28.698791221374048</v>
+        <v>27.85685975609756</v>
       </c>
       <c r="AE39" s="6">
-        <v>0.2786259541984733</v>
+        <v>0.28658536585365851</v>
       </c>
       <c r="AF39" s="9"/>
       <c r="AG39" s="5">
-        <v>-594.34000000000003</v>
+        <v>-702.13999999999999</v>
       </c>
       <c r="AH39" s="10">
         <v>2</v>
@@ -6493,7 +6491,7 @@
         <v>36621.666666666664</v>
       </c>
       <c r="Q40" s="6">
-        <v>-0.041157484766653041</v>
+        <v>-0.093124735651205159</v>
       </c>
       <c r="R40" s="7">
         <v>438.66666666666663</v>
@@ -6529,7 +6527,7 @@
         <v>9.8217759124087589</v>
       </c>
       <c r="AC40" s="8">
-        <v>14.541124999999999</v>
+        <v>13.153701</v>
       </c>
       <c r="AD40" s="8">
         <v>19.876343727598567</v>
@@ -6622,7 +6620,7 @@
         <v>72704.279999999999</v>
       </c>
       <c r="Q41" s="6">
-        <v>0.23164424483307378</v>
+        <v>0.09143920681210127</v>
       </c>
       <c r="R41" s="7">
         <v>864</v>
@@ -6658,7 +6656,7 @@
         <v>6.8929765112262515</v>
       </c>
       <c r="AC41" s="8">
-        <v>12.584496</v>
+        <v>14.145365</v>
       </c>
       <c r="AD41" s="8">
         <v>22.316188701517707</v>
@@ -6753,7 +6751,7 @@
         <v>70930.850000000006</v>
       </c>
       <c r="Q42" s="6">
-        <v>0.25287979616439338</v>
+        <v>0.10530450984703443</v>
       </c>
       <c r="R42" s="7">
         <v>727</v>
@@ -6789,7 +6787,7 @@
         <v>6.9119462427745662</v>
       </c>
       <c r="AC42" s="8">
-        <v>12.995437000000001</v>
+        <v>12.75591</v>
       </c>
       <c r="AD42" s="8">
         <v>19.369615730337078</v>
@@ -6936,7 +6934,7 @@
         <v>19622</v>
       </c>
       <c r="B44" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C44" s="4">
         <v>44</v>
@@ -6973,59 +6971,59 @@
         <v>52</v>
       </c>
       <c r="O44" s="5">
-        <v>33104.900000000001</v>
+        <v>40353.950000000004</v>
       </c>
       <c r="P44" s="5">
-        <v>38622.383333333339</v>
+        <v>40353.950000000004</v>
       </c>
       <c r="Q44" s="6">
-        <v>0.28803532818640143</v>
+        <v>0.21574261196089295</v>
       </c>
       <c r="R44" s="7">
-        <v>435.16666666666663</v>
+        <v>464.00000000000006</v>
       </c>
       <c r="S44" s="6">
-        <v>0.37638376383763839</v>
+        <v>0.18670076726342733</v>
       </c>
       <c r="T44" s="6">
-        <v>0.2673280028032104</v>
+        <v>0.28338701911460962</v>
       </c>
       <c r="U44" s="6">
-        <v>-0.07704971771550434</v>
+        <v>-0.065439551766307891</v>
       </c>
       <c r="V44" s="6">
-        <v>0.041753909542091953</v>
+        <v>0.040542648241374143</v>
       </c>
       <c r="W44" s="6">
-        <v>0.018910765475805696</v>
+        <v>0.019119714426964401</v>
       </c>
       <c r="X44" s="8">
-        <v>24.777031707317072</v>
+        <v>24.714890532544377</v>
       </c>
       <c r="Y44" s="6">
-        <v>0.87804878048780488</v>
+        <v>0.88165680473372776</v>
       </c>
       <c r="Z44" s="6">
         <v>0</v>
       </c>
       <c r="AA44" s="8">
-        <v>4.9017271708683472</v>
+        <v>4.5593302483069982</v>
       </c>
       <c r="AB44" s="8">
-        <v>2.9988174193548387</v>
+        <v>3.01125</v>
       </c>
       <c r="AC44" s="8">
         <v>8.2633620000000008</v>
       </c>
       <c r="AD44" s="8">
-        <v>14.777134146341462</v>
+        <v>14.736587573964496</v>
       </c>
       <c r="AE44" s="6">
-        <v>0.87195121951219512</v>
+        <v>0.87573964497041423</v>
       </c>
       <c r="AF44" s="9"/>
       <c r="AG44" s="5">
-        <v>-734.5</v>
+        <v>-1074.9000000000001</v>
       </c>
       <c r="AH44" s="10">
         <v>1</v>
@@ -7110,7 +7108,7 @@
         <v>30556.969999999998</v>
       </c>
       <c r="Q45" s="6">
-        <v>-0.00087203485262066227</v>
+        <v>-0.093504117163157874</v>
       </c>
       <c r="R45" s="7">
         <v>342</v>
@@ -7146,7 +7144,7 @@
         <v>6.0889481283422455</v>
       </c>
       <c r="AC45" s="8">
-        <v>11.193146</v>
+        <v>11.137425</v>
       </c>
       <c r="AD45" s="8">
         <v>18.671111282051282</v>
@@ -7239,7 +7237,7 @@
         <v>28257.32</v>
       </c>
       <c r="Q46" s="6">
-        <v>-0.088918508831493326</v>
+        <v>-0.17266260141773293</v>
       </c>
       <c r="R46" s="7">
         <v>315</v>
@@ -7275,7 +7273,7 @@
         <v>5.0245681481481483</v>
       </c>
       <c r="AC46" s="8">
-        <v>8.2040209999999991</v>
+        <v>7.889049</v>
       </c>
       <c r="AD46" s="8">
         <v>14.255172413793103</v>
@@ -7368,7 +7366,7 @@
         <v>52251.570000000007</v>
       </c>
       <c r="Q47" s="6">
-        <v>-0.19993847750034288</v>
+        <v>-0.24526731828352522</v>
       </c>
       <c r="R47" s="7">
         <v>458</v>
@@ -7404,7 +7402,7 @@
         <v>5.859072177419355</v>
       </c>
       <c r="AC47" s="8">
-        <v>9.6351980000000008</v>
+        <v>9.7772360000000003</v>
       </c>
       <c r="AD47" s="8">
         <v>16.119423076923077</v>
@@ -7499,7 +7497,7 @@
         <v>52389.130000000005</v>
       </c>
       <c r="Q48" s="6">
-        <v>0.091483412885093429</v>
+        <v>-0.022380743025366523</v>
       </c>
       <c r="R48" s="7">
         <v>572</v>
@@ -7535,7 +7533,7 @@
         <v>11.988591711229946</v>
       </c>
       <c r="AC48" s="8">
-        <v>15.048353000000001</v>
+        <v>16.938075000000001</v>
       </c>
       <c r="AD48" s="8">
         <v>22.349740932642487</v>
@@ -7628,7 +7626,7 @@
         <v>30951.029999999999</v>
       </c>
       <c r="Q49" s="6">
-        <v>-0.18346474848385408</v>
+        <v>-0.26298508017121991</v>
       </c>
       <c r="R49" s="7">
         <v>355</v>
@@ -7664,7 +7662,7 @@
         <v>12.518662275449101</v>
       </c>
       <c r="AC49" s="8">
-        <v>19.323923000000001</v>
+        <v>19.07949</v>
       </c>
       <c r="AD49" s="8">
         <v>25.567630057803466</v>
@@ -7852,7 +7850,7 @@
         <v>51790.559999999998</v>
       </c>
       <c r="Q51" s="6">
-        <v>0.30580885777124345</v>
+        <v>0.17615040754908229</v>
       </c>
       <c r="R51" s="7">
         <v>576</v>
@@ -7888,7 +7886,7 @@
         <v>14.407997986577183</v>
       </c>
       <c r="AC51" s="8">
-        <v>22.750471000000001</v>
+        <v>21.243338999999999</v>
       </c>
       <c r="AD51" s="8">
         <v>27.680819672131147</v>
@@ -7983,7 +7981,7 @@
         <v>26495.326666666671</v>
       </c>
       <c r="Q52" s="6">
-        <v>0.20839433380491834</v>
+        <v>0.45449119054176101</v>
       </c>
       <c r="R52" s="7">
         <v>317.33333333333337</v>
@@ -8112,7 +8110,7 @@
         <v>41136.139999999999</v>
       </c>
       <c r="Q53" s="6">
-        <v>0.22118240786094923</v>
+        <v>0.10747500005384447</v>
       </c>
       <c r="R53" s="7">
         <v>456</v>
@@ -8148,7 +8146,7 @@
         <v>12.857002801120448</v>
       </c>
       <c r="AC53" s="8">
-        <v>16.737000999999999</v>
+        <v>18.478567000000002</v>
       </c>
       <c r="AD53" s="8">
         <v>26.40247422969188</v>
@@ -8243,7 +8241,7 @@
         <v>44500.260000000002</v>
       </c>
       <c r="Q54" s="6">
-        <v>0.26378612206228258</v>
+        <v>0.14051790487316107</v>
       </c>
       <c r="R54" s="7">
         <v>480</v>
@@ -8279,7 +8277,7 @@
         <v>9.8039249999999996</v>
       </c>
       <c r="AC54" s="8">
-        <v>16.691583999999999</v>
+        <v>19.811533000000001</v>
       </c>
       <c r="AD54" s="8">
         <v>26.754046014492751</v>
@@ -8331,7 +8329,7 @@
         <v>19649</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>44</v>
@@ -8366,59 +8364,59 @@
         <v>52</v>
       </c>
       <c r="O55" s="5">
-        <v>40450.989999999998</v>
+        <v>52961.279999999999</v>
       </c>
       <c r="P55" s="5">
-        <v>47192.821666666663</v>
+        <v>52961.279999999992</v>
       </c>
       <c r="Q55" s="6">
-        <v>-0.06974482754315825</v>
+        <v>-0.072258231100564951</v>
       </c>
       <c r="R55" s="7">
-        <v>549.5</v>
+        <v>613</v>
       </c>
       <c r="S55" s="6">
-        <v>-0.10626185958254264</v>
+        <v>-0.14025245441795231</v>
       </c>
       <c r="T55" s="6">
-        <v>0.26625787156259961</v>
+        <v>0.26360836633857793</v>
       </c>
       <c r="U55" s="6">
-        <v>-0.051187511109122431</v>
+        <v>-0.051490513446804907</v>
       </c>
       <c r="V55" s="6">
-        <v>0.048352920410600589</v>
+        <v>0.045591175288814775</v>
       </c>
       <c r="W55" s="6">
-        <v>0.0076241273699358169</v>
+        <v>0.0079463147416376639</v>
       </c>
       <c r="X55" s="8">
-        <v>23.88190720720721</v>
+        <v>23.857565248226951</v>
       </c>
       <c r="Y55" s="6">
-        <v>0.97297297297297303</v>
+        <v>0.97163120567375882</v>
       </c>
       <c r="Z55" s="6">
-        <v>0.04954954954954955</v>
+        <v>0.042553191489361701</v>
       </c>
       <c r="AA55" s="8">
-        <v>2.7074688741721857</v>
+        <v>2.8590757983193278</v>
       </c>
       <c r="AB55" s="8">
-        <v>6.2404301435406699</v>
+        <v>5.7892853383458647</v>
       </c>
       <c r="AC55" s="8">
-        <v>8.7975560000000002</v>
+        <v>8.9123140000000003</v>
       </c>
       <c r="AD55" s="8">
-        <v>16.178528828828828</v>
+        <v>15.892553546099291</v>
       </c>
       <c r="AE55" s="6">
-        <v>0.81981981981981977</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="AF55" s="9"/>
       <c r="AG55" s="5">
-        <v>-1395.7</v>
+        <v>-1491</v>
       </c>
       <c r="AH55" s="10">
         <v>5</v>
@@ -8501,7 +8499,7 @@
         <v>115602.97</v>
       </c>
       <c r="Q56" s="6">
-        <v>0.19908289111372746</v>
+        <v>0.072447536073341423</v>
       </c>
       <c r="R56" s="7">
         <v>1111</v>
@@ -8537,7 +8535,7 @@
         <v>6.5050361459521095</v>
       </c>
       <c r="AC56" s="8">
-        <v>15.011906</v>
+        <v>14.54659</v>
       </c>
       <c r="AD56" s="8">
         <v>21.404143019296253</v>
@@ -8630,7 +8628,7 @@
         <v>33828.030000000006</v>
       </c>
       <c r="Q57" s="6">
-        <v>-0.12862730329605654</v>
+        <v>-0.21495861293697271</v>
       </c>
       <c r="R57" s="7">
         <v>390</v>
@@ -8666,7 +8664,7 @@
         <v>4.4745206896551721</v>
       </c>
       <c r="AC57" s="8">
-        <v>7.882333</v>
+        <v>7.6493370000000001</v>
       </c>
       <c r="AD57" s="8">
         <v>15.282965745856355</v>
@@ -8809,7 +8807,7 @@
         <v>19657</v>
       </c>
       <c r="B59" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C59" s="4">
         <v>44</v>
@@ -8846,59 +8844,59 @@
         <v>52</v>
       </c>
       <c r="O59" s="5">
-        <v>31959.989999999998</v>
+        <v>42969.440000000002</v>
       </c>
       <c r="P59" s="5">
-        <v>37286.654999999999</v>
+        <v>42969.440000000002</v>
       </c>
       <c r="Q59" s="6">
-        <v>0.3175245065995207</v>
+        <v>0.37358563908207332</v>
       </c>
       <c r="R59" s="7">
-        <v>374.5</v>
+        <v>433</v>
       </c>
       <c r="S59" s="6">
-        <v>0.14234875444839834</v>
+        <v>0.21288515406162456</v>
       </c>
       <c r="T59" s="6">
         <v>0</v>
       </c>
       <c r="U59" s="6">
-        <v>-0.31465404088048837</v>
+        <v>-0.30688577742693407</v>
       </c>
       <c r="V59" s="6">
-        <v>0.048016066337943163</v>
+        <v>0.042860204833947105</v>
       </c>
       <c r="W59" s="6">
-        <v>0.024970689915735266</v>
+        <v>0.022459659702337285</v>
       </c>
       <c r="X59" s="8">
-        <v>33.022249753694581</v>
+        <v>34.879545454545458</v>
       </c>
       <c r="Y59" s="6">
-        <v>0.51724137931034486</v>
+        <v>0.47924528301886793</v>
       </c>
       <c r="Z59" s="6">
-        <v>0.22167487684729065</v>
+        <v>0.26893939393939392</v>
       </c>
       <c r="AA59" s="8">
-        <v>9.1216201238390102</v>
+        <v>9.4038489607390296</v>
       </c>
       <c r="AB59" s="8">
-        <v>10.9495</v>
+        <v>12.286068702290075</v>
       </c>
       <c r="AC59" s="8">
-        <v>20.370090999999999</v>
+        <v>20.141532000000002</v>
       </c>
       <c r="AD59" s="8">
-        <v>26.791954187192118</v>
+        <v>28.31289320754717</v>
       </c>
       <c r="AE59" s="6">
-        <v>0.48768472906403942</v>
+        <v>0.4621212121212121</v>
       </c>
       <c r="AF59" s="9"/>
       <c r="AG59" s="5">
-        <v>-2015.52</v>
+        <v>-2554.3200000000002</v>
       </c>
       <c r="AH59" s="10">
         <v>3</v>
@@ -9074,7 +9072,7 @@
         <v>59954.241666666669</v>
       </c>
       <c r="Q61" s="6">
-        <v>0.28949992594055129</v>
+        <v>0.15679692633435716</v>
       </c>
       <c r="R61" s="7">
         <v>584.5</v>
@@ -9205,7 +9203,7 @@
         <v>58944.43</v>
       </c>
       <c r="Q62" s="6">
-        <v>0.29656539376419566</v>
+        <v>0.16217741846441625</v>
       </c>
       <c r="R62" s="7">
         <v>609</v>
@@ -9241,7 +9239,7 @@
         <v>16.130838323353291</v>
       </c>
       <c r="AC62" s="8">
-        <v>23.196235999999999</v>
+        <v>23.674643</v>
       </c>
       <c r="AD62" s="8">
         <v>30.528224404761904</v>
@@ -9293,7 +9291,7 @@
         <v>19674</v>
       </c>
       <c r="B63" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C63" s="4">
         <v>44</v>
@@ -9328,59 +9326,59 @@
         <v>52</v>
       </c>
       <c r="O63" s="5">
-        <v>37680.830000000002</v>
+        <v>42355.510000000002</v>
       </c>
       <c r="P63" s="5">
-        <v>43960.968333333331</v>
+        <v>42355.510000000002</v>
       </c>
       <c r="Q63" s="6">
-        <v>-0.030041393697143537</v>
+        <v>-0.19413647402279621</v>
       </c>
       <c r="R63" s="7">
-        <v>519.16666666666674</v>
+        <v>500</v>
       </c>
       <c r="S63" s="6">
-        <v>-0.10282258064516125</v>
+        <v>-0.13793103448275867</v>
       </c>
       <c r="T63" s="6">
-        <v>0.10524891038758966</v>
+        <v>0.21546210870793434</v>
       </c>
       <c r="U63" s="6">
-        <v>-0.31300514611806585</v>
+        <v>-0.20310539289929455</v>
       </c>
       <c r="V63" s="6">
-        <v>0.031601533193403648</v>
+        <v>0.032277890172966874</v>
       </c>
       <c r="W63" s="6">
-        <v>-0.0010986488354953964</v>
+        <v>-0.001329543665039094</v>
       </c>
       <c r="X63" s="8">
-        <v>29.017832167832168</v>
+        <v>28.685838343558284</v>
       </c>
       <c r="Y63" s="6">
-        <v>0.73426573426573427</v>
+        <v>0.71165644171779141</v>
       </c>
       <c r="Z63" s="6">
-        <v>0.097902097902097904</v>
+        <v>0.09815950920245399</v>
       </c>
       <c r="AA63" s="8">
-        <v>5.3390389639639642</v>
+        <v>5.2546370967741938</v>
       </c>
       <c r="AB63" s="8">
-        <v>5.9304621722846438</v>
+        <v>5.9705850993377485</v>
       </c>
       <c r="AC63" s="8">
         <v>11.347011999999999</v>
       </c>
       <c r="AD63" s="8">
-        <v>20.714277622377622</v>
+        <v>20.601687423312882</v>
       </c>
       <c r="AE63" s="6">
-        <v>0.63286713286713292</v>
+        <v>0.64110429447852757</v>
       </c>
       <c r="AF63" s="9"/>
       <c r="AG63" s="5">
-        <v>-345.60000000000002</v>
+        <v>-397.5</v>
       </c>
       <c r="AH63" s="10">
         <v>3</v>
@@ -9467,7 +9465,7 @@
         <v>13202.42</v>
       </c>
       <c r="Q64" s="6">
-        <v>-0.028938220899597522</v>
+        <v>-0.10474769701264308</v>
       </c>
       <c r="R64" s="7">
         <v>169</v>
@@ -9503,7 +9501,7 @@
         <v>6.9756589928057551</v>
       </c>
       <c r="AC64" s="8">
-        <v>11.791069</v>
+        <v>11.906067999999999</v>
       </c>
       <c r="AD64" s="8">
         <v>18.493749999999999</v>
@@ -9598,7 +9596,7 @@
         <v>56771.399999999987</v>
       </c>
       <c r="Q65" s="6">
-        <v>0.39547231160666585</v>
+        <v>0.2568589220060451</v>
       </c>
       <c r="R65" s="7">
         <v>577</v>
@@ -9634,7 +9632,7 @@
         <v>8.1585358490566033</v>
       </c>
       <c r="AC65" s="8">
-        <v>14.976525000000001</v>
+        <v>14.604647</v>
       </c>
       <c r="AD65" s="8">
         <v>21.399059408602149</v>
@@ -9822,7 +9820,7 @@
         <v>32084.329999999998</v>
       </c>
       <c r="Q67" s="6">
-        <v>0.029300631997690063</v>
+        <v>-0.066406820595638183</v>
       </c>
       <c r="R67" s="7">
         <v>331</v>
@@ -9858,7 +9856,7 @@
         <v>11.269444017094017</v>
       </c>
       <c r="AC67" s="8">
-        <v>16.714492</v>
+        <v>19.950105000000001</v>
       </c>
       <c r="AD67" s="8">
         <v>25.386937065637067</v>
@@ -9953,7 +9951,7 @@
         <v>35763.910000000003</v>
       </c>
       <c r="Q68" s="6">
-        <v>0.68679945458567349</v>
+        <v>0.63620363567156168</v>
       </c>
       <c r="R68" s="7">
         <v>430</v>
@@ -9989,7 +9987,7 @@
         <v>14.620772463768116</v>
       </c>
       <c r="AC68" s="8">
-        <v>19.153103999999999</v>
+        <v>19.588902000000001</v>
       </c>
       <c r="AD68" s="8">
         <v>20.476975257731958</v>
@@ -10084,7 +10082,7 @@
         <v>34533.020000000004</v>
       </c>
       <c r="Q69" s="6">
-        <v>-0.0613063146569649</v>
+        <v>-0.13058205374159393</v>
       </c>
       <c r="R69" s="7">
         <v>401</v>
@@ -10120,7 +10118,7 @@
         <v>5.1125338842975205</v>
       </c>
       <c r="AC69" s="8">
-        <v>12.913379000000001</v>
+        <v>15.982891</v>
       </c>
       <c r="AD69" s="8">
         <v>24.128848995983937</v>
@@ -10215,7 +10213,7 @@
         <v>43004.040000000001</v>
       </c>
       <c r="Q70" s="6">
-        <v>-0.12461751414729472</v>
+        <v>-0.17468953009701293</v>
       </c>
       <c r="R70" s="7">
         <v>425</v>
@@ -10251,7 +10249,7 @@
         <v>4.7639540697674416</v>
       </c>
       <c r="AC70" s="8">
-        <v>8.8395170000000007</v>
+        <v>8.8396190000000008</v>
       </c>
       <c r="AD70" s="8">
         <v>13.836309821428571</v>
@@ -10344,7 +10342,7 @@
         <v>58291.340000000004</v>
       </c>
       <c r="Q71" s="6">
-        <v>0.18240242665835305</v>
+        <v>-0.0038192034086406146</v>
       </c>
       <c r="R71" s="7">
         <v>526</v>
@@ -10380,7 +10378,7 @@
         <v>8.2772598870056502</v>
       </c>
       <c r="AC71" s="8">
-        <v>11.43149</v>
+        <v>12.066905999999999</v>
       </c>
       <c r="AD71" s="8">
         <v>18.29380309859155</v>
@@ -10525,7 +10523,7 @@
         <v>19694</v>
       </c>
       <c r="B73" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C73" s="4">
         <v>44</v>
@@ -10562,59 +10560,59 @@
         <v>52</v>
       </c>
       <c r="O73" s="5">
-        <v>35574.700000000004</v>
+        <v>45400.590000000004</v>
       </c>
       <c r="P73" s="5">
-        <v>41503.816666666673</v>
+        <v>45400.590000000004</v>
       </c>
       <c r="Q73" s="6">
-        <v>0.22285991694352836</v>
+        <v>0.20816233445863097</v>
       </c>
       <c r="R73" s="7">
-        <v>439.83333333333337</v>
+        <v>480</v>
       </c>
       <c r="S73" s="6">
-        <v>0.056022408963585457</v>
+        <v>0.083521444695259683</v>
       </c>
       <c r="T73" s="6">
-        <v>-9.4845163866455664</v>
+        <v>-6.9036687254504843</v>
       </c>
       <c r="U73" s="6">
-        <v>-15.220146202216744</v>
+        <v>-12.564613660307058</v>
       </c>
       <c r="V73" s="6">
-        <v>0.090585669028832291</v>
+        <v>0.088878580652806502</v>
       </c>
       <c r="W73" s="6">
-        <v>0.058854972775596148</v>
+        <v>0.058569282910200068</v>
       </c>
       <c r="X73" s="8">
-        <v>47.320050957854406</v>
+        <v>44.813831671554254</v>
       </c>
       <c r="Y73" s="6">
-        <v>0.37593984962406013</v>
+        <v>0.38150289017341038</v>
       </c>
       <c r="Z73" s="6">
-        <v>0.48659003831417624</v>
+        <v>0.44281524926686217</v>
       </c>
       <c r="AA73" s="8">
-        <v>10.870098128342246</v>
+        <v>9.9846262054507324</v>
       </c>
       <c r="AB73" s="8">
-        <v>19.378617441860463</v>
+        <v>18.361770326409495</v>
       </c>
       <c r="AC73" s="8">
-        <v>24.180171999999999</v>
+        <v>30.727805</v>
       </c>
       <c r="AD73" s="8">
-        <v>37.445338697318007</v>
+        <v>35.364614076246333</v>
       </c>
       <c r="AE73" s="6">
-        <v>0.28735632183908044</v>
+        <v>0.30498533724340177</v>
       </c>
       <c r="AF73" s="9"/>
       <c r="AG73" s="5">
-        <v>-2788.1399999999999</v>
+        <v>-3314.5300000000002</v>
       </c>
       <c r="AH73" s="10">
         <v>2</v>
@@ -10699,7 +10697,7 @@
         <v>50651.099999999999</v>
       </c>
       <c r="Q74" s="6">
-        <v>0.099558340994617467</v>
+        <v>-0.013994549347868368</v>
       </c>
       <c r="R74" s="7">
         <v>571</v>
@@ -10735,7 +10733,7 @@
         <v>4.819258536585366</v>
       </c>
       <c r="AC74" s="8">
-        <v>12.084446</v>
+        <v>11.680697</v>
       </c>
       <c r="AD74" s="8">
         <v>18.348175147928995</v>
@@ -10830,7 +10828,7 @@
         <v>33485.209999999999</v>
       </c>
       <c r="Q75" s="6">
-        <v>0.042840107469316768</v>
+        <v>-0.056292364062282996</v>
       </c>
       <c r="R75" s="7">
         <v>398</v>
@@ -10866,7 +10864,7 @@
         <v>5.7990251461988302</v>
       </c>
       <c r="AC75" s="8">
-        <v>11.497325</v>
+        <v>12.13531</v>
       </c>
       <c r="AD75" s="8">
         <v>20.037036842105262</v>
@@ -10959,7 +10957,7 @@
         <v>40580.629999999997</v>
       </c>
       <c r="Q76" s="6">
-        <v>0.047481836487474727</v>
+        <v>-0.062365150654647428</v>
       </c>
       <c r="R76" s="7">
         <v>450.00000000000006</v>
@@ -10995,7 +10993,7 @@
         <v>5.9487574561403509</v>
       </c>
       <c r="AC76" s="8">
-        <v>9.698537</v>
+        <v>11.499718</v>
       </c>
       <c r="AD76" s="8">
         <v>18.471957539682538</v>
@@ -11183,7 +11181,7 @@
         <v>31932.25</v>
       </c>
       <c r="Q78" s="6">
-        <v>0.088348369637458735</v>
+        <v>-0.10359801575905703</v>
       </c>
       <c r="R78" s="7">
         <v>340</v>
@@ -11219,7 +11217,7 @@
         <v>10.399289573459717</v>
       </c>
       <c r="AC78" s="8">
-        <v>17.901115000000001</v>
+        <v>19.16459</v>
       </c>
       <c r="AD78" s="8">
         <v>24.921615720524017</v>
@@ -11271,7 +11269,7 @@
         <v>19715</v>
       </c>
       <c r="B79" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C79" s="4">
         <v>44</v>
@@ -11308,59 +11306,59 @@
         <v>52</v>
       </c>
       <c r="O79" s="5">
-        <v>35423.25</v>
+        <v>45795.970000000001</v>
       </c>
       <c r="P79" s="5">
-        <v>41327.125</v>
+        <v>45795.970000000008</v>
       </c>
       <c r="Q79" s="6">
-        <v>0.46970570412086765</v>
+        <v>0.46607060423430768</v>
       </c>
       <c r="R79" s="7">
-        <v>443.33333333333337</v>
+        <v>487.99999999999994</v>
       </c>
       <c r="S79" s="6">
-        <v>0.24590163934426235</v>
+        <v>0.29787234042553168</v>
       </c>
       <c r="T79" s="6">
-        <v>0.27349972122828931</v>
+        <v>0.21155243572742316</v>
       </c>
       <c r="U79" s="6">
-        <v>-0.11046448307255828</v>
+        <v>-0.16390854915836481</v>
       </c>
       <c r="V79" s="6">
-        <v>0.044682828368373874</v>
+        <v>0.046124986543575774</v>
       </c>
       <c r="W79" s="6">
-        <v>0.016710804344604181</v>
+        <v>0.020420759730605115</v>
       </c>
       <c r="X79" s="8">
-        <v>33.95368852459017</v>
+        <v>33.959158785942492</v>
       </c>
       <c r="Y79" s="6">
         <v>1</v>
       </c>
       <c r="Z79" s="6">
-        <v>0.24180327868852458</v>
+        <v>0.24281150159744408</v>
       </c>
       <c r="AA79" s="8">
-        <v>10.671378795811519</v>
+        <v>10.634972745901639</v>
       </c>
       <c r="AB79" s="8">
-        <v>10.182304115226337</v>
+        <v>10.075294533762058</v>
       </c>
       <c r="AC79" s="8">
         <v>20.764688</v>
       </c>
       <c r="AD79" s="8">
-        <v>29.682991803278686</v>
+        <v>29.712779552715656</v>
       </c>
       <c r="AE79" s="6">
-        <v>0.42213114754098363</v>
+        <v>0.41853035143769968</v>
       </c>
       <c r="AF79" s="9"/>
       <c r="AG79" s="5">
-        <v>-870.70000000000005</v>
+        <v>-922.60000000000002</v>
       </c>
       <c r="AH79" s="10">
         <v>3</v>
@@ -11443,7 +11441,7 @@
         <v>31900.200000000001</v>
       </c>
       <c r="Q80" s="6">
-        <v>0.070145770384387962</v>
+        <v>-0.17770867251563882</v>
       </c>
       <c r="R80" s="7">
         <v>371</v>
@@ -11479,7 +11477,7 @@
         <v>16.362500000000001</v>
       </c>
       <c r="AC80" s="8">
-        <v>19.440407</v>
+        <v>22.169362</v>
       </c>
       <c r="AD80" s="8">
         <v>27.915158371040725</v>
@@ -11669,7 +11667,7 @@
         <v>33380.279999999999</v>
       </c>
       <c r="Q82" s="6">
-        <v>0.048871733929427563</v>
+        <v>-0.00063500161220342299</v>
       </c>
       <c r="R82" s="7">
         <v>359</v>
@@ -11705,7 +11703,7 @@
         <v>7.1645025974025973</v>
       </c>
       <c r="AC82" s="8">
-        <v>13.627894</v>
+        <v>13.45425</v>
       </c>
       <c r="AD82" s="8">
         <v>18.17731330798479</v>
@@ -11800,7 +11798,7 @@
         <v>44824.270000000004</v>
       </c>
       <c r="Q83" s="6">
-        <v>0.04263292536045582</v>
+        <v>-0.013773946486601685</v>
       </c>
       <c r="R83" s="7">
         <v>492.00000000000006</v>
@@ -11836,7 +11834,7 @@
         <v>5.3242049469964661</v>
       </c>
       <c r="AC83" s="8">
-        <v>14.810473999999999</v>
+        <v>13.519636999999999</v>
       </c>
       <c r="AD83" s="8">
         <v>21.747001384083045</v>
@@ -11929,7 +11927,7 @@
         <v>36790.290000000001</v>
       </c>
       <c r="Q84" s="6">
-        <v>0.22894631795019116</v>
+        <v>0.11347487679689783</v>
       </c>
       <c r="R84" s="7">
         <v>332</v>
@@ -11965,7 +11963,7 @@
         <v>9.6844999999999999</v>
       </c>
       <c r="AC84" s="8">
-        <v>13.244956</v>
+        <v>13.163387999999999</v>
       </c>
       <c r="AD84" s="8">
         <v>18.923076923076923</v>
@@ -12060,7 +12058,7 @@
         <v>20634.34</v>
       </c>
       <c r="Q85" s="6">
-        <v>0.24695065942141081</v>
+        <v>0.17936527714112938</v>
       </c>
       <c r="R85" s="7">
         <v>245</v>
@@ -12096,7 +12094,7 @@
         <v>1.0893330000000001</v>
       </c>
       <c r="AC85" s="8">
-        <v>6.529865</v>
+        <v>6.698556</v>
       </c>
       <c r="AD85" s="8">
         <v>13.738166000000001</v>
@@ -12191,7 +12189,7 @@
         <v>35792.420000000006</v>
       </c>
       <c r="Q86" s="6">
-        <v>0.016909848613130052</v>
+        <v>-0.078300293615800376</v>
       </c>
       <c r="R86" s="7">
         <v>386</v>
@@ -12227,7 +12225,7 @@
         <v>12.027328676470589</v>
       </c>
       <c r="AC86" s="8">
-        <v>19.294011999999999</v>
+        <v>20.358699999999999</v>
       </c>
       <c r="AD86" s="8">
         <v>27.301102573529413</v>
@@ -12372,7 +12370,7 @@
         <v>19730</v>
       </c>
       <c r="B88" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C88" s="4">
         <v>44</v>
@@ -12407,59 +12405,59 @@
         <v>52</v>
       </c>
       <c r="O88" s="5">
-        <v>47665.760000000002</v>
+        <v>60363.690000000002</v>
       </c>
       <c r="P88" s="5">
-        <v>55610.053333333337</v>
+        <v>60363.690000000002</v>
       </c>
       <c r="Q88" s="6">
-        <v>0.051183839294226319</v>
+        <v>0.013236906022818351</v>
       </c>
       <c r="R88" s="7">
-        <v>561.16666666666674</v>
+        <v>619</v>
       </c>
       <c r="S88" s="6">
-        <v>-0.056862745098039125</v>
+        <v>-0.060698027314112335</v>
       </c>
       <c r="T88" s="6">
-        <v>-0.00052868138470885595</v>
+        <v>0.24685222026685247</v>
       </c>
       <c r="U88" s="6">
-        <v>-0.34188755198700282</v>
+        <v>-0.091059030685499837</v>
       </c>
       <c r="V88" s="6">
-        <v>0.032894167637314502</v>
+        <v>0.032573298617099122</v>
       </c>
       <c r="W88" s="6">
-        <v>0.014627386618822399</v>
+        <v>0.016322635345851121</v>
       </c>
       <c r="X88" s="8">
-        <v>27.81497536231884</v>
+        <v>27.264328658536588</v>
       </c>
       <c r="Y88" s="6">
-        <v>0.49275362318840582</v>
+        <v>0.53658536585365857</v>
       </c>
       <c r="Z88" s="6">
-        <v>0.13043478260869565</v>
+        <v>0.11585365853658537</v>
       </c>
       <c r="AA88" s="8">
-        <v>4.6924708418891168</v>
+        <v>4.7800637958532697</v>
       </c>
       <c r="AB88" s="8">
-        <v>10.530676811594203</v>
+        <v>10.157927439024391</v>
       </c>
       <c r="AC88" s="8">
         <v>15.556694999999999</v>
       </c>
       <c r="AD88" s="8">
-        <v>23.505434057971012</v>
+        <v>23.089938414634144</v>
       </c>
       <c r="AE88" s="6">
-        <v>0.71739130434782605</v>
+        <v>0.73780487804878048</v>
       </c>
       <c r="AF88" s="9"/>
       <c r="AG88" s="5">
-        <v>-273.94</v>
+        <v>-390.83999999999997</v>
       </c>
       <c r="AH88" s="10">
         <v>2</v>
@@ -12637,7 +12635,7 @@
         <v>18195.739999999998</v>
       </c>
       <c r="Q90" s="6">
-        <v>-0.088449605762347505</v>
+        <v>-0.13785594274781332</v>
       </c>
       <c r="R90" s="7">
         <v>206</v>
@@ -12673,7 +12671,7 @@
         <v>1.6637060913705581</v>
       </c>
       <c r="AC90" s="8">
-        <v>7.5359699999999998</v>
+        <v>7.5370379999999999</v>
       </c>
       <c r="AD90" s="8">
         <v>14.464057070707071</v>
@@ -12766,7 +12764,7 @@
         <v>21446.600000000002</v>
       </c>
       <c r="Q91" s="6">
-        <v>-0.64656974935268341</v>
+        <v>-0.081476329382983992</v>
       </c>
       <c r="R91" s="7">
         <v>217</v>
@@ -12895,7 +12893,7 @@
         <v>89218.110000000001</v>
       </c>
       <c r="Q92" s="6">
-        <v>0.015061963666565203</v>
+        <v>-0.062996297171106663</v>
       </c>
       <c r="R92" s="7">
         <v>833</v>
@@ -12931,7 +12929,7 @@
         <v>4.9756666666666671</v>
       </c>
       <c r="AC92" s="8">
-        <v>7.214645</v>
+        <v>12.479785</v>
       </c>
       <c r="AD92" s="8">
         <v>20.988619142857143</v>
@@ -13026,7 +13024,7 @@
         <v>49380.840000000004</v>
       </c>
       <c r="Q93" s="6">
-        <v>0.22460719247333216</v>
+        <v>0.0991025039212452</v>
       </c>
       <c r="R93" s="7">
         <v>438</v>
@@ -13062,7 +13060,7 @@
         <v>4.5323621359223303</v>
       </c>
       <c r="AC93" s="8">
-        <v>10.178216000000001</v>
+        <v>9.2328270000000003</v>
       </c>
       <c r="AD93" s="8">
         <v>17.035699053627759</v>
@@ -13157,7 +13155,7 @@
         <v>30571.809999999998</v>
       </c>
       <c r="Q94" s="6">
-        <v>0.064039777487197913</v>
+        <v>-0.034103877130880256</v>
       </c>
       <c r="R94" s="7">
         <v>324</v>
@@ -13193,7 +13191,7 @@
         <v>4.2943584615384616</v>
       </c>
       <c r="AC94" s="8">
-        <v>7.3908880000000003</v>
+        <v>8.0506080000000004</v>
       </c>
       <c r="AD94" s="8">
         <v>15.576842788461537</v>
@@ -13286,7 +13284,7 @@
         <v>26422.849999999999</v>
       </c>
       <c r="Q95" s="6">
-        <v>-0.16205109795301853</v>
+        <v>-0.24421581403650472</v>
       </c>
       <c r="R95" s="7">
         <v>258</v>
@@ -13322,7 +13320,7 @@
         <v>17.618278709677419</v>
       </c>
       <c r="AC95" s="8">
-        <v>17.744194</v>
+        <v>24.869931000000001</v>
       </c>
       <c r="AD95" s="8">
         <v>31.703885276073621</v>
@@ -13417,7 +13415,7 @@
         <v>46892.959999999999</v>
       </c>
       <c r="Q96" s="6">
-        <v>0.18840670797908099</v>
+        <v>0.068512166233501093</v>
       </c>
       <c r="R96" s="7">
         <v>546</v>
@@ -13453,7 +13451,7 @@
         <v>11.03481261682243</v>
       </c>
       <c r="AC96" s="8">
-        <v>19.169063999999999</v>
+        <v>20.822129</v>
       </c>
       <c r="AD96" s="8">
         <v>24.41764705882353</v>
@@ -13505,7 +13503,7 @@
         <v>19749</v>
       </c>
       <c r="B97" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C97" s="4">
         <v>44</v>
@@ -13540,59 +13538,59 @@
         <v>52</v>
       </c>
       <c r="O97" s="5">
-        <v>21825.869999999999</v>
+        <v>26916.73</v>
       </c>
       <c r="P97" s="5">
-        <v>25463.514999999999</v>
+        <v>26916.73</v>
       </c>
       <c r="Q97" s="6">
-        <v>-0.11194829643858817</v>
+        <v>-0.14825757642880377</v>
       </c>
       <c r="R97" s="7">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="S97" s="6">
-        <v>-0.25252525252525249</v>
+        <v>-0.24444444444444446</v>
       </c>
       <c r="T97" s="6">
-        <v>13.633300899345594</v>
+        <v>3.7516655292080427</v>
       </c>
       <c r="U97" s="6">
-        <v>9.8465867843985144</v>
+        <v>0.0114229365899944</v>
       </c>
       <c r="V97" s="6">
-        <v>0.034403302136409679</v>
+        <v>0.031277294827417743</v>
       </c>
       <c r="W97" s="6">
-        <v>0.022100928851862493</v>
+        <v>0.019401409457983937</v>
       </c>
       <c r="X97" s="8">
-        <v>32.523581481481479</v>
+        <v>34.023810714285716</v>
       </c>
       <c r="Y97" s="6">
-        <v>0.71014492753623193</v>
+        <v>0.68421052631578949</v>
       </c>
       <c r="Z97" s="6">
-        <v>0.17037037037037037</v>
+        <v>0.22023809523809523</v>
       </c>
       <c r="AA97" s="8">
-        <v>4.0960031674208146</v>
+        <v>4.5509914498141262</v>
       </c>
       <c r="AB97" s="8">
-        <v>9.9660591240875913</v>
+        <v>11.026275294117646</v>
       </c>
       <c r="AC97" s="8">
-        <v>11.770383000000001</v>
+        <v>13.999271999999999</v>
       </c>
       <c r="AD97" s="8">
-        <v>21.850483333333333</v>
+        <v>23.265789473684208</v>
       </c>
       <c r="AE97" s="6">
-        <v>0.40740740740740738</v>
+        <v>0.35119047619047616</v>
       </c>
       <c r="AF97" s="9"/>
       <c r="AG97" s="5">
-        <v>-458.30000000000001</v>
+        <v>-544.89999999999998</v>
       </c>
       <c r="AH97" s="10">
         <v>1</v>
@@ -13675,7 +13673,7 @@
         <v>22284.149999999998</v>
       </c>
       <c r="Q98" s="6">
-        <v>-0.0047586721272672161</v>
+        <v>-0.093549945940405221</v>
       </c>
       <c r="R98" s="7">
         <v>248</v>
@@ -13711,7 +13709,7 @@
         <v>3.9675542553191492</v>
       </c>
       <c r="AC98" s="8">
-        <v>9.6152300000000004</v>
+        <v>9.9619970000000002</v>
       </c>
       <c r="AD98" s="8">
         <v>16.13585462184874</v>
@@ -13806,7 +13804,7 @@
         <v>50448.440000000002</v>
       </c>
       <c r="Q99" s="6">
-        <v>0.17111180598453157</v>
+        <v>0.045153693101068093</v>
       </c>
       <c r="R99" s="7">
         <v>592</v>
@@ -13842,7 +13840,7 @@
         <v>5.0445274626865668</v>
       </c>
       <c r="AC99" s="8">
-        <v>8.8756789999999999</v>
+        <v>8.8261339999999997</v>
       </c>
       <c r="AD99" s="8">
         <v>15.659931268436578</v>
@@ -13937,7 +13935,7 @@
         <v>60491.260000000002</v>
       </c>
       <c r="Q100" s="6">
-        <v>-0.0054760972334431113</v>
+        <v>-0.14240343201608274</v>
       </c>
       <c r="R100" s="7">
         <v>538</v>
@@ -13973,7 +13971,7 @@
         <v>5.6011242063492066</v>
       </c>
       <c r="AC100" s="8">
-        <v>8.6203500000000002</v>
+        <v>8.3577899999999996</v>
       </c>
       <c r="AD100" s="8">
         <v>16.208104705882356</v>
@@ -14068,7 +14066,7 @@
         <v>18562.290000000001</v>
       </c>
       <c r="Q101" s="6">
-        <v>-0.1851314493871461</v>
+        <v>-0.25625444499426031</v>
       </c>
       <c r="R101" s="7">
         <v>186</v>
@@ -14104,7 +14102,7 @@
         <v>13.042079207920793</v>
       </c>
       <c r="AC101" s="8">
-        <v>17.650455000000001</v>
+        <v>19.455068000000001</v>
       </c>
       <c r="AD101" s="8">
         <v>27.579537623762377</v>
@@ -14199,7 +14197,7 @@
         <v>39323.059999999998</v>
       </c>
       <c r="Q102" s="6">
-        <v>-0.055158631855063311</v>
+        <v>-0.24961190665608457</v>
       </c>
       <c r="R102" s="7">
         <v>425</v>
@@ -14235,7 +14233,7 @@
         <v>15.542129938271604</v>
       </c>
       <c r="AC102" s="8">
-        <v>22.518536000000001</v>
+        <v>21.103823999999999</v>
       </c>
       <c r="AD102" s="8">
         <v>28.286078143712576</v>
@@ -14330,7 +14328,7 @@
         <v>24217.029999999999</v>
       </c>
       <c r="Q103" s="6">
-        <v>-0.24582842454416387</v>
+        <v>-0.31646653972798688</v>
       </c>
       <c r="R103" s="7">
         <v>304</v>
@@ -14366,7 +14364,7 @@
         <v>15.977831553398058</v>
       </c>
       <c r="AC103" s="8">
-        <v>22.980739</v>
+        <v>20.90729</v>
       </c>
       <c r="AD103" s="8">
         <v>26.475942081447965</v>
@@ -14461,7 +14459,7 @@
         <v>30325.759999999998</v>
       </c>
       <c r="Q104" s="6">
-        <v>0.30606000963854596</v>
+        <v>0.18669386569975233</v>
       </c>
       <c r="R104" s="7">
         <v>337</v>
@@ -14497,7 +14495,7 @@
         <v>7.0182799999999999</v>
       </c>
       <c r="AC104" s="8">
-        <v>13.148921</v>
+        <v>14.523122000000001</v>
       </c>
       <c r="AD104" s="8">
         <v>24.259177215189872</v>
@@ -14592,7 +14590,7 @@
         <v>23508.540000000001</v>
       </c>
       <c r="Q105" s="6">
-        <v>-0.0071627247748344836</v>
+        <v>-0.095666778481149017</v>
       </c>
       <c r="R105" s="7">
         <v>310</v>
@@ -14628,7 +14626,7 @@
         <v>11.752475247524753</v>
       </c>
       <c r="AC105" s="8">
-        <v>21.333012</v>
+        <v>21.121478</v>
       </c>
       <c r="AD105" s="8">
         <v>28.191913861386137</v>
@@ -14723,7 +14721,7 @@
         <v>24454.820000000003</v>
       </c>
       <c r="Q106" s="6">
-        <v>-0.017618324535820684</v>
+        <v>-0.21849610123993346</v>
       </c>
       <c r="R106" s="7">
         <v>272</v>
@@ -14759,7 +14757,7 @@
         <v>17.930434299516907</v>
       </c>
       <c r="AC106" s="8">
-        <v>26.443352000000001</v>
+        <v>24.592189000000001</v>
       </c>
       <c r="AD106" s="8">
         <v>31.504348309178742</v>
@@ -14854,7 +14852,7 @@
         <v>28946.43</v>
       </c>
       <c r="Q107" s="6">
-        <v>-0.24251766368346672</v>
+        <v>-0.28584589096099988</v>
       </c>
       <c r="R107" s="7">
         <v>287</v>
@@ -14890,7 +14888,7 @@
         <v>9.1969088709677411</v>
       </c>
       <c r="AC107" s="8">
-        <v>10.707098</v>
+        <v>12.135832000000001</v>
       </c>
       <c r="AD107" s="8">
         <v>16.81036081081081</v>
@@ -14985,7 +14983,7 @@
         <v>28911.310000000001</v>
       </c>
       <c r="Q108" s="6">
-        <v>0.22972115390341163</v>
+        <v>0.11870938284168719</v>
       </c>
       <c r="R108" s="7">
         <v>278</v>
@@ -15019,7 +15017,7 @@
         <v>15.08802676056338</v>
       </c>
       <c r="AC108" s="8">
-        <v>25.257708999999998</v>
+        <v>27.695333000000002</v>
       </c>
       <c r="AD108" s="8">
         <v>34.165752054794524</v>
@@ -15114,7 +15112,7 @@
         <v>77535.669999999998</v>
       </c>
       <c r="Q109" s="6">
-        <v>0.21676132899601841</v>
+        <v>-0.083342899619023525</v>
       </c>
       <c r="R109" s="7">
         <v>926</v>
@@ -15150,7 +15148,7 @@
         <v>12.712983150183149</v>
       </c>
       <c r="AC109" s="8">
-        <v>18.588522999999999</v>
+        <v>21.209050999999999</v>
       </c>
       <c r="AD109" s="8">
         <v>26.496481839622639</v>
@@ -15245,7 +15243,7 @@
         <v>36590.519999999997</v>
       </c>
       <c r="Q110" s="6">
-        <v>0.20421346955660624</v>
+        <v>0.14548412060377025</v>
       </c>
       <c r="R110" s="7">
         <v>368</v>
@@ -15281,7 +15279,7 @@
         <v>10.461367630057804</v>
       </c>
       <c r="AC110" s="8">
-        <v>16.852446</v>
+        <v>17.365414999999999</v>
       </c>
       <c r="AD110" s="8">
         <v>22.255555050505052</v>
@@ -15376,7 +15374,7 @@
         <v>30629.950000000004</v>
       </c>
       <c r="Q111" s="6">
-        <v>0.36769789678708831</v>
+        <v>0.23942260535716331</v>
       </c>
       <c r="R111" s="7">
         <v>319</v>
@@ -15412,7 +15410,7 @@
         <v>25.711626050420168</v>
       </c>
       <c r="AC111" s="8">
-        <v>31.959648999999999</v>
+        <v>41.766824</v>
       </c>
       <c r="AD111" s="8">
         <v>46.541057723577239</v>
@@ -15507,7 +15505,7 @@
         <v>25328.43</v>
       </c>
       <c r="Q112" s="6">
-        <v>0.061873809877170505</v>
+        <v>0.011752717581261951</v>
       </c>
       <c r="R112" s="7">
         <v>349</v>
@@ -15543,7 +15541,7 @@
         <v>3.585934682080925</v>
       </c>
       <c r="AC112" s="8">
-        <v>6.7603920000000004</v>
+        <v>6.7793510000000001</v>
       </c>
       <c r="AD112" s="8">
         <v>13.133246073298428</v>
@@ -15595,7 +15593,7 @@
         <v>19785</v>
       </c>
       <c r="B113" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C113" s="4">
         <v>44</v>
@@ -15632,59 +15630,59 @@
         <v>52</v>
       </c>
       <c r="O113" s="5">
-        <v>24592.82</v>
+        <v>32935.220000000001</v>
       </c>
       <c r="P113" s="5">
-        <v>28691.623333333333</v>
+        <v>32935.220000000001</v>
       </c>
       <c r="Q113" s="6">
-        <v>-0.18039974081263133</v>
+        <v>-0.15483993645239402</v>
       </c>
       <c r="R113" s="7">
-        <v>275.33333333333337</v>
+        <v>313</v>
       </c>
       <c r="S113" s="6">
-        <v>-0.23376623376623373</v>
+        <v>-0.20153061224489799</v>
       </c>
       <c r="T113" s="6">
-        <v>0.26442743451137368</v>
+        <v>0.26394348967457931</v>
       </c>
       <c r="U113" s="6">
-        <v>-0.011423809876215904</v>
+        <v>-0.01045303781180147</v>
       </c>
       <c r="V113" s="6">
-        <v>0.013606166352618364</v>
+        <v>0.012979251391064033</v>
       </c>
       <c r="W113" s="6">
-        <v>-0.0086909919236590194</v>
+        <v>-0.0068818577802121856</v>
       </c>
       <c r="X113" s="8">
-        <v>24.433005882352941</v>
+        <v>25.114178358208957</v>
       </c>
       <c r="Y113" s="6">
-        <v>0.61764705882352944</v>
+        <v>0.58955223880597019</v>
       </c>
       <c r="Z113" s="6">
-        <v>0.078431372549019607</v>
+        <v>0.067164179104477612</v>
       </c>
       <c r="AA113" s="8">
-        <v>5.9534901709401709</v>
+        <v>6.0343012903225803</v>
       </c>
       <c r="AB113" s="8">
-        <v>6.0622340425531913</v>
+        <v>6.8461745901639341</v>
       </c>
       <c r="AC113" s="8">
         <v>11.783149</v>
       </c>
       <c r="AD113" s="8">
-        <v>17.999347058823528</v>
+        <v>18.645896268656717</v>
       </c>
       <c r="AE113" s="6">
-        <v>0.75490196078431371</v>
+        <v>0.78358208955223885</v>
       </c>
       <c r="AF113" s="9"/>
       <c r="AG113" s="5">
-        <v>-1439.8</v>
+        <v>-2245.9000000000001</v>
       </c>
       <c r="AH113" s="10">
         <v>4</v>
@@ -15767,7 +15765,7 @@
         <v>23131</v>
       </c>
       <c r="Q114" s="6">
-        <v>0.33234645270172969</v>
+        <v>0.21881434987786053</v>
       </c>
       <c r="R114" s="7">
         <v>250</v>
@@ -15803,7 +15801,7 @@
         <v>8.5633341176470594</v>
       </c>
       <c r="AC114" s="8">
-        <v>18.328769000000001</v>
+        <v>16.536272</v>
       </c>
       <c r="AD114" s="8">
         <v>23.359018823529411</v>
@@ -15896,7 +15894,7 @@
         <v>103341.67</v>
       </c>
       <c r="Q115" s="6">
-        <v>0.0423727668124525</v>
+        <v>-0.069421275653873238</v>
       </c>
       <c r="R115" s="7">
         <v>989.99999999999989</v>
@@ -15932,7 +15930,7 @@
         <v>8.7335768924302783</v>
       </c>
       <c r="AC115" s="8">
-        <v>23.011071999999999</v>
+        <v>19.950907999999998</v>
       </c>
       <c r="AD115" s="8">
         <v>25.9296875</v>
@@ -16027,7 +16025,7 @@
         <v>57346.929999999993</v>
       </c>
       <c r="Q116" s="6">
-        <v>-0.12797112038520353</v>
+        <v>-0.19503036940328422</v>
       </c>
       <c r="R116" s="7">
         <v>536</v>
@@ -16063,7 +16061,7 @@
         <v>4.0636961240310079</v>
       </c>
       <c r="AC116" s="8">
-        <v>9.0476559999999999</v>
+        <v>9.1729149999999997</v>
       </c>
       <c r="AD116" s="8">
         <v>11.379459459459458</v>
@@ -16249,7 +16247,7 @@
         <v>59478.346666666672</v>
       </c>
       <c r="Q118" s="6">
-        <v>0.016180174823840821</v>
+        <v>-0.020988243933341977</v>
       </c>
       <c r="R118" s="7">
         <v>590.33333333333326</v>
@@ -16378,7 +16376,7 @@
         <v>51559.5</v>
       </c>
       <c r="Q119" s="6">
-        <v>-0.0068680096293902704</v>
+        <v>-0.053744042255253199</v>
       </c>
       <c r="R119" s="7">
         <v>637</v>
@@ -16414,7 +16412,7 @@
         <v>10.326561213720318</v>
       </c>
       <c r="AC119" s="8">
-        <v>16.829689999999999</v>
+        <v>17.483060999999999</v>
       </c>
       <c r="AD119" s="8">
         <v>24.92783426395939</v>
@@ -16509,7 +16507,7 @@
         <v>57742.75</v>
       </c>
       <c r="Q120" s="6">
-        <v>0.26764971066515963</v>
+        <v>0.096770266063338717</v>
       </c>
       <c r="R120" s="7">
         <v>711</v>
@@ -16545,7 +16543,7 @@
         <v>2.3400205702647656</v>
       </c>
       <c r="AC120" s="8">
-        <v>4.6162539999999996</v>
+        <v>5.5718350000000001</v>
       </c>
       <c r="AD120" s="8">
         <v>12.295808383233533</v>
@@ -16640,7 +16638,7 @@
         <v>44353.840000000004</v>
       </c>
       <c r="Q121" s="6">
-        <v>-0.041757810618046176</v>
+        <v>-0.27691686437650931</v>
       </c>
       <c r="R121" s="7">
         <v>572</v>
@@ -16676,7 +16674,7 @@
         <v>18.607718066157762</v>
       </c>
       <c r="AC121" s="8">
-        <v>25.167394999999999</v>
+        <v>24.372914999999999</v>
       </c>
       <c r="AD121" s="8">
         <v>31.787138213399505</v>
@@ -16771,7 +16769,7 @@
         <v>30556.699999999993</v>
       </c>
       <c r="Q122" s="6">
-        <v>0.11510872754397039</v>
+        <v>-0.1579285892623199</v>
       </c>
       <c r="R122" s="7">
         <v>329</v>
@@ -16807,7 +16805,7 @@
         <v>13.481587142857142</v>
       </c>
       <c r="AC122" s="8">
-        <v>24.226220999999999</v>
+        <v>22.031721000000001</v>
       </c>
       <c r="AD122" s="8">
         <v>27.778943303571427</v>
@@ -16900,7 +16898,7 @@
         <v>36879.549999999996</v>
       </c>
       <c r="Q123" s="6">
-        <v>0.35072906564154538</v>
+        <v>0.072635904016529418</v>
       </c>
       <c r="R123" s="7">
         <v>392</v>
@@ -16936,7 +16934,7 @@
         <v>2.7100003076923076</v>
       </c>
       <c r="AC123" s="8">
-        <v>8.3745790000000007</v>
+        <v>8.3426799999999997</v>
       </c>
       <c r="AD123" s="8">
         <v>15.18549156626506</v>
@@ -17085,7 +17083,7 @@
         <v>19842</v>
       </c>
       <c r="B125" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C125" s="4">
         <v>44</v>
@@ -17122,59 +17120,59 @@
         <v>52</v>
       </c>
       <c r="O125" s="5">
-        <v>59565.230000000003</v>
+        <v>73176.419999999998</v>
       </c>
       <c r="P125" s="5">
-        <v>69492.768333333341</v>
+        <v>73176.419999999998</v>
       </c>
       <c r="Q125" s="6">
-        <v>-0.06589840576846473</v>
+        <v>-0.069597581903385275</v>
       </c>
       <c r="R125" s="7">
-        <v>670.83333333333326</v>
+        <v>704</v>
       </c>
       <c r="S125" s="6">
-        <v>-0.17857142857142871</v>
+        <v>-0.16090584028605481</v>
       </c>
       <c r="T125" s="6">
-        <v>0.3193696540750367</v>
+        <v>0.31213947471056935</v>
       </c>
       <c r="U125" s="6">
-        <v>0.0024772321033596279</v>
+        <v>-0.0031732995410270141</v>
       </c>
       <c r="V125" s="6">
-        <v>0.022342396730441565</v>
+        <v>0.022532442827894558</v>
       </c>
       <c r="W125" s="6">
-        <v>0.006622991298782863</v>
+        <v>0.0071615077643863963</v>
       </c>
       <c r="X125" s="8">
-        <v>30.355660377358493</v>
+        <v>31.857730425531916</v>
       </c>
       <c r="Y125" s="6">
-        <v>0.89218328840970351</v>
+        <v>0.86808510638297876</v>
       </c>
       <c r="Z125" s="6">
-        <v>0.094339622641509441</v>
+        <v>0.17659574468085107</v>
       </c>
       <c r="AA125" s="8">
-        <v>5.2493296160877509</v>
+        <v>5.6162474852071007</v>
       </c>
       <c r="AB125" s="8">
-        <v>10.803698314606741</v>
+        <v>12.127111538461538</v>
       </c>
       <c r="AC125" s="8">
         <v>16.041734999999999</v>
       </c>
       <c r="AD125" s="8">
-        <v>23.108266037735849</v>
+        <v>24.334610000000001</v>
       </c>
       <c r="AE125" s="6">
-        <v>0.49865229110512127</v>
+        <v>0.4297872340425532</v>
       </c>
       <c r="AF125" s="9"/>
       <c r="AG125" s="5">
-        <v>-12527.23</v>
+        <v>-15050.43</v>
       </c>
       <c r="AH125" s="10">
         <v>3</v>
@@ -17258,9 +17256,7 @@
       <c r="P126" s="5">
         <v>31508.790000000001</v>
       </c>
-      <c r="Q126" s="6">
-        <v>-0.016381267883599615</v>
-      </c>
+      <c r="Q126" s="6"/>
       <c r="R126" s="7">
         <v>282</v>
       </c>
@@ -17388,7 +17384,7 @@
         <v>22860.809999999998</v>
       </c>
       <c r="Q127" s="6">
-        <v>-0.17213931032884389</v>
+        <v>0.3613126972151246</v>
       </c>
       <c r="R127" s="7">
         <v>255.5</v>
@@ -17476,7 +17472,7 @@
         <v>19859</v>
       </c>
       <c r="B128" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C128" s="4">
         <v>44</v>
@@ -17513,55 +17509,55 @@
         <v>52</v>
       </c>
       <c r="O128" s="5">
-        <v>26699.169999999998</v>
+        <v>33140.529999999999</v>
       </c>
       <c r="P128" s="5">
-        <v>31149.031666666666</v>
+        <v>33140.529999999999</v>
       </c>
       <c r="Q128" s="6">
-        <v>-0.16213654917922682</v>
+        <v>-0.25580414084254022</v>
       </c>
       <c r="R128" s="7">
-        <v>324.33333333333337</v>
+        <v>342</v>
       </c>
       <c r="S128" s="6">
-        <v>-0.28534704370179942</v>
+        <v>-0.25652173913043474</v>
       </c>
       <c r="T128" s="6">
-        <v>0.31403266094039634</v>
+        <v>0.31312669109395652</v>
       </c>
       <c r="U128" s="6">
-        <v>-0.0034461221079157144</v>
+        <v>-0.0064560071911945885</v>
       </c>
       <c r="V128" s="6">
-        <v>0.033880678687764454</v>
+        <v>0.031411990091890503</v>
       </c>
       <c r="W128" s="6">
-        <v>-0.0010440024914632178</v>
+        <v>-0.00096769725770831064</v>
       </c>
       <c r="X128" s="8">
-        <v>32.859555555555552</v>
+        <v>33.740553429602883</v>
       </c>
       <c r="Y128" s="6">
-        <v>0.5377777777777778</v>
+        <v>0.48014440433212996</v>
       </c>
       <c r="Z128" s="6">
-        <v>0.24444444444444444</v>
+        <v>0.27436823104693142</v>
       </c>
       <c r="AA128" s="8">
-        <v>7.7264039426523308</v>
+        <v>8.4790574344023319</v>
       </c>
       <c r="AB128" s="8">
-        <v>6.4111848888888883</v>
+        <v>6.6187122743682307</v>
       </c>
       <c r="AC128" s="8">
         <v>14.606527</v>
       </c>
       <c r="AD128" s="8">
-        <v>21.516518222222221</v>
+        <v>22.525511191335742</v>
       </c>
       <c r="AE128" s="6">
-        <v>0.49333333333333335</v>
+        <v>0.44043321299638988</v>
       </c>
       <c r="AF128" s="9"/>
       <c r="AG128" s="5">
@@ -17650,7 +17646,7 @@
         <v>23924.600000000002</v>
       </c>
       <c r="Q129" s="6">
-        <v>-0.51089110894543488</v>
+        <v>-0.27661627941431688</v>
       </c>
       <c r="R129" s="7">
         <v>266</v>
@@ -17777,7 +17773,7 @@
         <v>30892.790000000001</v>
       </c>
       <c r="Q130" s="6">
-        <v>-0.27780829821275455</v>
+        <v>-0.40929580039404767</v>
       </c>
       <c r="R130" s="7">
         <v>330</v>
@@ -17813,7 +17809,7 @@
         <v>6.8444036900369003</v>
       </c>
       <c r="AC130" s="8">
-        <v>15.564484</v>
+        <v>15.25713</v>
       </c>
       <c r="AD130" s="8">
         <v>22.11428608058608</v>
@@ -17906,7 +17902,7 @@
         <v>27992.049999999996</v>
       </c>
       <c r="Q131" s="6">
-        <v>-0.10089447863086454</v>
+        <v>-0.18066205502070465</v>
       </c>
       <c r="R131" s="7">
         <v>386</v>
@@ -18033,7 +18029,7 @@
         <v>46571.709999999999</v>
       </c>
       <c r="Q132" s="6">
-        <v>0.13726007794719486</v>
+        <v>0.081306779871947343</v>
       </c>
       <c r="R132" s="7">
         <v>438</v>
@@ -18069,7 +18065,7 @@
         <v>20.878299999999999</v>
       </c>
       <c r="AC132" s="8">
-        <v>12.373507</v>
+        <v>33.936579000000002</v>
       </c>
       <c r="AD132" s="8">
         <v>41.309105853658536</v>
@@ -18164,7 +18160,7 @@
         <v>95195.540000000008</v>
       </c>
       <c r="Q133" s="6">
-        <v>0.22782938614554049</v>
+        <v>0.082478491554680344</v>
       </c>
       <c r="R133" s="7">
         <v>936</v>
@@ -18200,7 +18196,7 @@
         <v>10.087470014347202</v>
       </c>
       <c r="AC133" s="8">
-        <v>15.282496999999999</v>
+        <v>15.255405</v>
       </c>
       <c r="AD133" s="8">
         <v>21.543576026490065</v>
@@ -18295,7 +18291,7 @@
         <v>53476.639999999999</v>
       </c>
       <c r="Q134" s="6">
-        <v>0.013305875591645311</v>
+        <v>-0.036549115751267958</v>
       </c>
       <c r="R134" s="7">
         <v>573</v>
@@ -18331,7 +18327,7 @@
         <v>18.074267905405407</v>
       </c>
       <c r="AC134" s="8">
-        <v>18.184743999999998</v>
+        <v>27.508686999999998</v>
       </c>
       <c r="AD134" s="8">
         <v>33.974889403973513</v>
@@ -18426,7 +18422,7 @@
         <v>32976.720000000001</v>
       </c>
       <c r="Q135" s="6">
-        <v>0.00019108036840309595</v>
+        <v>-0.10052705410766993</v>
       </c>
       <c r="R135" s="7">
         <v>303</v>
@@ -18462,7 +18458,7 @@
         <v>18.40393354037267</v>
       </c>
       <c r="AC135" s="8">
-        <v>18.223018</v>
+        <v>22.2958</v>
       </c>
       <c r="AD135" s="8">
         <v>28.646161212121214</v>
@@ -18514,7 +18510,7 @@
         <v>19881</v>
       </c>
       <c r="B136" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C136" s="4">
         <v>44</v>
@@ -18551,55 +18547,55 @@
         <v>52</v>
       </c>
       <c r="O136" s="5">
-        <v>67218.869999999995</v>
+        <v>83003.489999999991</v>
       </c>
       <c r="P136" s="5">
-        <v>78422.014999999999</v>
+        <v>83003.489999999991</v>
       </c>
       <c r="Q136" s="6">
-        <v>0.047660585395035149</v>
+        <v>0.04887594290614361</v>
       </c>
       <c r="R136" s="7">
-        <v>681.33333333333326</v>
+        <v>724</v>
       </c>
       <c r="S136" s="6">
-        <v>-0.0017094017094018144</v>
+        <v>-0.016304347826086918</v>
       </c>
       <c r="T136" s="6">
-        <v>0.41146460510270405</v>
+        <v>0.56084603310053582</v>
       </c>
       <c r="U136" s="6">
-        <v>0.073268351580441635</v>
+        <v>0.22880023599007701</v>
       </c>
       <c r="V136" s="6">
-        <v>0.023480489927902689</v>
+        <v>0.023934029761881095</v>
       </c>
       <c r="W136" s="6">
-        <v>0.00039262784393727536</v>
+        <v>0.0009474059464246624</v>
       </c>
       <c r="X136" s="8">
-        <v>28.732517482517483</v>
+        <v>28.163054562737642</v>
       </c>
       <c r="Y136" s="6">
-        <v>0.66433566433566438</v>
+        <v>0.65019011406844107</v>
       </c>
       <c r="Z136" s="6">
-        <v>0.15384615384615385</v>
+        <v>0.12737642585551331</v>
       </c>
       <c r="AA136" s="8">
-        <v>3.1209524369747896</v>
+        <v>3.1766531250000001</v>
       </c>
       <c r="AB136" s="8">
-        <v>11.450879136690647</v>
+        <v>10.791018093385215</v>
       </c>
       <c r="AC136" s="8">
         <v>14.556537000000001</v>
       </c>
       <c r="AD136" s="8">
-        <v>20.42253333333333</v>
+        <v>19.870754372623573</v>
       </c>
       <c r="AE136" s="6">
-        <v>0.64568764568764569</v>
+        <v>0.66539923954372626</v>
       </c>
       <c r="AF136" s="9"/>
       <c r="AG136" s="5">
@@ -18688,7 +18684,7 @@
         <v>41997.939999999995</v>
       </c>
       <c r="Q137" s="6">
-        <v>0.13939561322024185</v>
+        <v>0.035270435761769692</v>
       </c>
       <c r="R137" s="7">
         <v>435</v>
@@ -18724,7 +18720,7 @@
         <v>5.2049126865671642</v>
       </c>
       <c r="AC137" s="8">
-        <v>7.8281049999999999</v>
+        <v>8.9859670000000005</v>
       </c>
       <c r="AD137" s="8">
         <v>15.59897761732852</v>
@@ -18776,7 +18772,7 @@
         <v>19884</v>
       </c>
       <c r="B138" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C138" s="4">
         <v>44</v>
@@ -18813,55 +18809,55 @@
         <v>52</v>
       </c>
       <c r="O138" s="5">
-        <v>24094.919999999998</v>
+        <v>30369.779999999999</v>
       </c>
       <c r="P138" s="5">
-        <v>28110.740000000002</v>
+        <v>30369.779999999999</v>
       </c>
       <c r="Q138" s="6">
-        <v>-0.1630681928137705</v>
+        <v>-0.27808809148118752</v>
       </c>
       <c r="R138" s="7">
-        <v>312.66666666666663</v>
+        <v>332</v>
       </c>
       <c r="S138" s="6">
-        <v>-0.26775956284153013</v>
+        <v>-0.25225225225225223</v>
       </c>
       <c r="T138" s="6">
-        <v>0.33085894039075459</v>
+        <v>0.32507659587919308</v>
       </c>
       <c r="U138" s="6">
-        <v>0.0052048191070980937</v>
+        <v>0.0051358521530284387</v>
       </c>
       <c r="V138" s="6">
-        <v>0.025698113959291006</v>
+        <v>0.026690611522375202</v>
       </c>
       <c r="W138" s="6">
-        <v>-0.02978910077310902</v>
+        <v>-0.025498768841921149</v>
       </c>
       <c r="X138" s="8">
-        <v>33.494764397905762</v>
+        <v>34.616391322314051</v>
       </c>
       <c r="Y138" s="6">
-        <v>0.50261780104712039</v>
+        <v>0.42561983471074383</v>
       </c>
       <c r="Z138" s="6">
-        <v>0.21989528795811519</v>
+        <v>0.27685950413223143</v>
       </c>
       <c r="AA138" s="8">
-        <v>8.3418503676470586</v>
+        <v>8.1235119047619051</v>
       </c>
       <c r="AB138" s="8">
-        <v>7.3381392638036811</v>
+        <v>7.931984285714285</v>
       </c>
       <c r="AC138" s="8">
         <v>17.119128</v>
       </c>
       <c r="AD138" s="8">
-        <v>22.418499476439791</v>
+        <v>22.579407851239669</v>
       </c>
       <c r="AE138" s="6">
-        <v>0.39267015706806285</v>
+        <v>0.33884297520661155</v>
       </c>
       <c r="AF138" s="9"/>
       <c r="AG138" s="5">
@@ -18950,7 +18946,7 @@
         <v>28583.41</v>
       </c>
       <c r="Q139" s="6">
-        <v>0.16856047907716798</v>
+        <v>-0.12054049846297554</v>
       </c>
       <c r="R139" s="7">
         <v>321</v>
@@ -18986,7 +18982,7 @@
         <v>3.5903450184501846</v>
       </c>
       <c r="AC139" s="8">
-        <v>9.6683959999999995</v>
+        <v>10.417719999999999</v>
       </c>
       <c r="AD139" s="8">
         <v>16.795172413793104</v>
@@ -19081,7 +19077,7 @@
         <v>42666.209999999999</v>
       </c>
       <c r="Q140" s="6">
-        <v>0.39309093509291304</v>
+        <v>0.058153515579079773</v>
       </c>
       <c r="R140" s="7">
         <v>491</v>
@@ -19117,7 +19113,7 @@
         <v>3.9811011160714287</v>
       </c>
       <c r="AC140" s="8">
-        <v>7.6955660000000004</v>
+        <v>8.7033229999999993</v>
       </c>
       <c r="AD140" s="8">
         <v>15.50519237472767</v>
@@ -19212,7 +19208,7 @@
         <v>33661.950000000004</v>
       </c>
       <c r="Q141" s="6">
-        <v>0.19360363379128054</v>
+        <v>0.083324241789370479</v>
       </c>
       <c r="R141" s="7">
         <v>429</v>
@@ -19248,7 +19244,7 @@
         <v>4.2235729281767949</v>
       </c>
       <c r="AC141" s="8">
-        <v>14.986720999999999</v>
+        <v>15.873025</v>
       </c>
       <c r="AD141" s="8">
         <v>22.850915384615387</v>
@@ -19341,7 +19337,7 @@
         <v>23892.950000000001</v>
       </c>
       <c r="Q142" s="6">
-        <v>-0.039485189034035972</v>
+        <v>-0.12395769703751669</v>
       </c>
       <c r="R142" s="7">
         <v>279</v>
@@ -19377,7 +19373,7 @@
         <v>11.412093292682927</v>
       </c>
       <c r="AC142" s="8">
-        <v>16.042065999999998</v>
+        <v>17.031735000000001</v>
       </c>
       <c r="AD142" s="8">
         <v>23.91676787878788</v>
@@ -19472,7 +19468,7 @@
         <v>20247.129999999997</v>
       </c>
       <c r="Q143" s="6">
-        <v>-0.079934781986341297</v>
+        <v>-0.16021997474910876</v>
       </c>
       <c r="R143" s="7">
         <v>283</v>
@@ -19508,7 +19504,7 @@
         <v>1.7067986842105263</v>
       </c>
       <c r="AC143" s="8">
-        <v>5.1856790000000004</v>
+        <v>5.1993299999999998</v>
       </c>
       <c r="AD143" s="8">
         <v>12.131808496732026</v>
@@ -19603,7 +19599,7 @@
         <v>33052.120000000003</v>
       </c>
       <c r="Q144" s="6">
-        <v>0.45669893088241653</v>
+        <v>0.3777457273864111</v>
       </c>
       <c r="R144" s="7">
         <v>391</v>
@@ -19639,7 +19635,7 @@
         <v>2.5454144104803493</v>
       </c>
       <c r="AC144" s="8">
-        <v>5.6572829999999996</v>
+        <v>6.3299110000000001</v>
       </c>
       <c r="AD144" s="8">
         <v>13.278165938864628</v>
@@ -19825,7 +19821,7 @@
         <v>15302.049999999999</v>
       </c>
       <c r="Q146" s="6">
-        <v>-0.37459614745619396</v>
+        <v>-0.43303692176587194</v>
       </c>
       <c r="R146" s="7">
         <v>184</v>
@@ -19913,7 +19909,7 @@
         <v>19910</v>
       </c>
       <c r="B147" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C147" s="4">
         <v>44</v>
@@ -19950,55 +19946,55 @@
         <v>52</v>
       </c>
       <c r="O147" s="5">
-        <v>22567.620000000003</v>
+        <v>28913.370000000003</v>
       </c>
       <c r="P147" s="5">
-        <v>26328.890000000003</v>
+        <v>28913.370000000003</v>
       </c>
       <c r="Q147" s="6">
-        <v>0.17656345867934253</v>
+        <v>0.19269738470423237</v>
       </c>
       <c r="R147" s="7">
-        <v>298.66666666666663</v>
+        <v>318</v>
       </c>
       <c r="S147" s="6">
-        <v>0.3128205128205126</v>
+        <v>0.18656716417910446</v>
       </c>
       <c r="T147" s="6">
-        <v>0.77320448500993899</v>
+        <v>0.59715297801674461</v>
       </c>
       <c r="U147" s="6">
-        <v>0.470842073732188</v>
+        <v>0.29133459710853493</v>
       </c>
       <c r="V147" s="6">
-        <v>0.074148226529868896</v>
+        <v>0.077485606139996818</v>
       </c>
       <c r="W147" s="6">
-        <v>0.043005819842765879</v>
+        <v>0.049097701167314635</v>
       </c>
       <c r="X147" s="8">
-        <v>23.571377536231886</v>
+        <v>21.734787209302326</v>
       </c>
       <c r="Y147" s="6">
-        <v>0.86956521739130432</v>
+        <v>0.88372093023255816</v>
       </c>
       <c r="Z147" s="6">
-        <v>0.043478260869565216</v>
+        <v>0.034883720930232558</v>
       </c>
       <c r="AA147" s="8">
-        <v>5.7935898785425097</v>
+        <v>5.2996226537216824</v>
       </c>
       <c r="AB147" s="8">
-        <v>9.7361523076923078</v>
+        <v>8.6948189189189193</v>
       </c>
       <c r="AC147" s="8">
         <v>15.836636</v>
       </c>
       <c r="AD147" s="8">
-        <v>17.1565700729927</v>
+        <v>15.721443274853799</v>
       </c>
       <c r="AE147" s="6">
-        <v>0.87681159420289856</v>
+        <v>0.90116279069767447</v>
       </c>
       <c r="AF147" s="9"/>
       <c r="AG147" s="5">
@@ -20087,7 +20083,7 @@
         <v>35665.68</v>
       </c>
       <c r="Q148" s="6">
-        <v>0.4526363635623103</v>
+        <v>0.31785074520978807</v>
       </c>
       <c r="R148" s="7">
         <v>487.99999999999994</v>
@@ -20123,7 +20119,7 @@
         <v>5.3270833333333334</v>
       </c>
       <c r="AC148" s="8">
-        <v>10.546341999999999</v>
+        <v>10.38672</v>
       </c>
       <c r="AD148" s="8">
         <v>16.400317391304348</v>
@@ -20218,7 +20214,7 @@
         <v>25428.941999999999</v>
       </c>
       <c r="Q149" s="6">
-        <v>0.40669988748145425</v>
+        <v>0.72404258772541752</v>
       </c>
       <c r="R149" s="7">
         <v>291.19999999999999</v>
@@ -20349,7 +20345,7 @@
         <v>51077.830000000002</v>
       </c>
       <c r="Q150" s="6">
-        <v>0.19506581564133407</v>
+        <v>0.0622150036964908</v>
       </c>
       <c r="R150" s="7">
         <v>567</v>
@@ -20385,7 +20381,7 @@
         <v>13.428954925373134</v>
       </c>
       <c r="AC150" s="8">
-        <v>20.853541</v>
+        <v>20.922374000000001</v>
       </c>
       <c r="AD150" s="8">
         <v>28.541504986149583</v>
@@ -20573,7 +20569,7 @@
         <v>18480.279999999999</v>
       </c>
       <c r="Q152" s="6">
-        <v>-0.033505674930207396</v>
+        <v>-0.10330819917125189</v>
       </c>
       <c r="R152" s="7">
         <v>233</v>
@@ -20609,7 +20605,7 @@
         <v>8.6577527131782954</v>
       </c>
       <c r="AC152" s="8">
-        <v>18.707615000000001</v>
+        <v>18.373208999999999</v>
       </c>
       <c r="AD152" s="8">
         <v>24.903579999999998</v>
@@ -20661,7 +20657,7 @@
         <v>19927</v>
       </c>
       <c r="B153" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C153" s="4">
         <v>44</v>
@@ -20698,55 +20694,55 @@
         <v>52</v>
       </c>
       <c r="O153" s="5">
-        <v>9928.7099999999991</v>
+        <v>12024.689999999999</v>
       </c>
       <c r="P153" s="5">
-        <v>11583.495000000001</v>
+        <v>12024.689999999999</v>
       </c>
       <c r="Q153" s="6">
-        <v>-0.042138561888286574</v>
+        <v>-0.078894614401174179</v>
       </c>
       <c r="R153" s="7">
-        <v>145.83333333333331</v>
+        <v>153</v>
       </c>
       <c r="S153" s="6">
-        <v>-0.094202898550724723</v>
+        <v>-0.089285714285714302</v>
       </c>
       <c r="T153" s="6">
-        <v>0</v>
+        <v>0.0037539429290900637</v>
       </c>
       <c r="U153" s="6">
-        <v>-0.32856332796506299</v>
+        <v>-0.32310687427285029</v>
       </c>
       <c r="V153" s="6">
-        <v>0.11971207739978305</v>
+        <v>0.11842434191650679</v>
       </c>
       <c r="W153" s="6">
-        <v>0.040599080847360837</v>
+        <v>0.042582885712646235</v>
       </c>
       <c r="X153" s="8">
-        <v>41.836184210526319</v>
+        <v>39.070297029702971</v>
       </c>
       <c r="Y153" s="6">
-        <v>0.39473684210526316</v>
+        <v>0.38613861386138615</v>
       </c>
       <c r="Z153" s="6">
-        <v>0.47368421052631576</v>
+        <v>0.36633663366336633</v>
       </c>
       <c r="AA153" s="8">
-        <v>9.8776452380952389</v>
+        <v>9.3715363636363627</v>
       </c>
       <c r="AB153" s="8">
-        <v>13.110086842105263</v>
+        <v>11.936833</v>
       </c>
       <c r="AC153" s="8">
-        <v>20.276723</v>
+        <v>22.270693000000001</v>
       </c>
       <c r="AD153" s="8">
-        <v>29.303288157894738</v>
+        <v>27.371286138613858</v>
       </c>
       <c r="AE153" s="6">
-        <v>0.25</v>
+        <v>0.29702970297029702</v>
       </c>
       <c r="AF153" s="9"/>
       <c r="AG153" s="5">
@@ -20837,7 +20833,7 @@
         <v>33281.089999999997</v>
       </c>
       <c r="Q154" s="6">
-        <v>0.21838507761459125</v>
+        <v>0.10940738651780824</v>
       </c>
       <c r="R154" s="7">
         <v>403</v>
@@ -20873,7 +20869,7 @@
         <v>10.920034246575343</v>
       </c>
       <c r="AC154" s="8">
-        <v>16.835080999999999</v>
+        <v>15.897866</v>
       </c>
       <c r="AD154" s="8">
         <v>22.284808852459015</v>
@@ -20925,7 +20921,7 @@
         <v>19930</v>
       </c>
       <c r="B155" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C155" s="4">
         <v>44</v>
@@ -20962,59 +20958,59 @@
         <v>52</v>
       </c>
       <c r="O155" s="5">
-        <v>25331.900000000001</v>
+        <v>32817.75</v>
       </c>
       <c r="P155" s="5">
-        <v>29553.883333333335</v>
+        <v>32817.75</v>
       </c>
       <c r="Q155" s="6">
-        <v>0.13390974164578839</v>
+        <v>0.14528651924192348</v>
       </c>
       <c r="R155" s="7">
-        <v>434</v>
+        <v>489</v>
       </c>
       <c r="S155" s="6">
-        <v>0.10714285714285721</v>
+        <v>0.093959731543624248</v>
       </c>
       <c r="T155" s="6">
-        <v>0.36031372301327574</v>
+        <v>0.35624995010322158</v>
       </c>
       <c r="U155" s="6">
-        <v>0.02115005980601534</v>
+        <v>0.017666713897205019</v>
       </c>
       <c r="V155" s="6">
-        <v>0.070759871940122926</v>
+        <v>0.067331855474552643</v>
       </c>
       <c r="W155" s="6">
-        <v>0.035357868932057994</v>
+        <v>0.034379870649267542</v>
       </c>
       <c r="X155" s="8">
-        <v>26.891980817610065</v>
+        <v>27.306496287703016</v>
       </c>
       <c r="Y155" s="6">
-        <v>0.20125786163522014</v>
+        <v>0.16937354988399073</v>
       </c>
       <c r="Z155" s="6">
-        <v>0.11006289308176101</v>
+        <v>0.092807424593967514</v>
       </c>
       <c r="AA155" s="8">
-        <v>4.7876114973262034</v>
+        <v>4.7551596741344193</v>
       </c>
       <c r="AB155" s="8">
-        <v>11.285649830508476</v>
+        <v>11.151474201474201</v>
       </c>
       <c r="AC155" s="8">
-        <v>15.752551</v>
+        <v>16.155801</v>
       </c>
       <c r="AD155" s="8">
-        <v>21.946173899371072</v>
+        <v>22.002474709976799</v>
       </c>
       <c r="AE155" s="6">
-        <v>0.68553459119496851</v>
+        <v>0.67517401392111365</v>
       </c>
       <c r="AF155" s="9"/>
       <c r="AG155" s="5">
-        <v>-142.80000000000001</v>
+        <v>-288.39999999999998</v>
       </c>
       <c r="AH155" s="10">
         <v>3</v>
@@ -21056,7 +21052,7 @@
         <v>19931</v>
       </c>
       <c r="B156" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C156" s="4">
         <v>44</v>
@@ -21093,59 +21089,59 @@
         <v>52</v>
       </c>
       <c r="O156" s="5">
-        <v>27539.369999999999</v>
+        <v>38774.639999999999</v>
       </c>
       <c r="P156" s="5">
-        <v>32129.264999999999</v>
+        <v>38774.639999999999</v>
       </c>
       <c r="Q156" s="6">
-        <v>-0.0086136565744335813</v>
+        <v>0.085253431070023478</v>
       </c>
       <c r="R156" s="7">
-        <v>337.16666666666663</v>
+        <v>408</v>
       </c>
       <c r="S156" s="6">
-        <v>-0.13213213213213226</v>
+        <v>-0.087248322147650992</v>
       </c>
       <c r="T156" s="6">
-        <v>0.26510358080086799</v>
+        <v>0.2906593072172946</v>
       </c>
       <c r="U156" s="6">
-        <v>-0.2154927436611658</v>
+        <v>-0.18787511631313664</v>
       </c>
       <c r="V156" s="6">
-        <v>0.060508791595450445</v>
+        <v>0.056857046254974904</v>
       </c>
       <c r="W156" s="6">
-        <v>0.03505977079359477</v>
+        <v>0.035419838843120138</v>
       </c>
       <c r="X156" s="8">
-        <v>25.966942148760332</v>
+        <v>25.358383233532937</v>
       </c>
       <c r="Y156" s="6">
-        <v>0.63636363636363635</v>
+        <v>0.67664670658682635</v>
       </c>
       <c r="Z156" s="6">
-        <v>0.024793388429752067</v>
+        <v>0.017964071856287425</v>
       </c>
       <c r="AA156" s="8">
-        <v>4.8154255319148938</v>
+        <v>4.7554020100502514</v>
       </c>
       <c r="AB156" s="8">
-        <v>4.6387461538461539</v>
+        <v>4.5362316770186339</v>
       </c>
       <c r="AC156" s="8">
-        <v>9.3288489999999999</v>
+        <v>9.7983080000000005</v>
       </c>
       <c r="AD156" s="8">
-        <v>16.492147933884297</v>
+        <v>16.282434730538924</v>
       </c>
       <c r="AE156" s="6">
-        <v>0.72727272727272729</v>
+        <v>0.77245508982035926</v>
       </c>
       <c r="AF156" s="9"/>
       <c r="AG156" s="5">
-        <v>-450.93000000000001</v>
+        <v>-520.73000000000002</v>
       </c>
       <c r="AH156" s="10">
         <v>2</v>
@@ -21230,7 +21226,7 @@
         <v>32373.709999999999</v>
       </c>
       <c r="Q157" s="6">
-        <v>1.6865101527160351</v>
+        <v>1.4644541140324567</v>
       </c>
       <c r="R157" s="7">
         <v>395</v>
@@ -21266,7 +21262,7 @@
         <v>5.3957399103139014</v>
       </c>
       <c r="AC157" s="8">
-        <v>9.2256830000000001</v>
+        <v>9.9522560000000002</v>
       </c>
       <c r="AD157" s="8">
         <v>14.280271768707484</v>
@@ -21360,9 +21356,7 @@
       <c r="P158" s="5">
         <v>17767.160000000003</v>
       </c>
-      <c r="Q158" s="6">
-        <v>-0.38896529476561836</v>
-      </c>
+      <c r="Q158" s="6"/>
       <c r="R158" s="7">
         <v>186</v>
       </c>
@@ -21397,7 +21391,7 @@
         <v>9.4322727272727267</v>
       </c>
       <c r="AC158" s="8">
-        <v>11.591604999999999</v>
+        <v>12.31649</v>
       </c>
       <c r="AD158" s="8">
         <v>19.082441071428573</v>
@@ -21490,7 +21484,7 @@
         <v>29909.59</v>
       </c>
       <c r="Q159" s="6">
-        <v>-0.16031023186255056</v>
+        <v>-0.23939016106788946</v>
       </c>
       <c r="R159" s="7">
         <v>357</v>
@@ -21526,7 +21520,7 @@
         <v>8.8420425806451615</v>
       </c>
       <c r="AC159" s="8">
-        <v>14.881057</v>
+        <v>14.658008000000001</v>
       </c>
       <c r="AD159" s="8">
         <v>19.480951648351649</v>
@@ -21580,7 +21574,7 @@
         <v>19943</v>
       </c>
       <c r="B160" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C160" s="4">
         <v>44</v>
@@ -21617,59 +21611,59 @@
         <v>52</v>
       </c>
       <c r="O160" s="5">
-        <v>16741.959999999999</v>
+        <v>22529.470000000001</v>
       </c>
       <c r="P160" s="5">
-        <v>19532.286666666667</v>
+        <v>22529.470000000001</v>
       </c>
       <c r="Q160" s="6">
-        <v>0.029637037009703437</v>
+        <v>0.09222567183397401</v>
       </c>
       <c r="R160" s="7">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="S160" s="6">
-        <v>-0.098591549295774628</v>
+        <v>-0.1202749140893471</v>
       </c>
       <c r="T160" s="6">
-        <v>0.36956023667479793</v>
+        <v>0.34990510207297371</v>
       </c>
       <c r="U160" s="6">
-        <v>0.024242245232935691</v>
+        <v>0.011285507382108855</v>
       </c>
       <c r="V160" s="6">
-        <v>0.059512267380880141</v>
+        <v>0.067012805893791549</v>
       </c>
       <c r="W160" s="6">
-        <v>0.018244697753429108</v>
+        <v>0.027645701385784927</v>
       </c>
       <c r="X160" s="8">
-        <v>33.923392105263162</v>
+        <v>32.70260816326531</v>
       </c>
       <c r="Y160" s="6">
-        <v>0.6228070175438597</v>
+        <v>0.65306122448979587</v>
       </c>
       <c r="Z160" s="6">
-        <v>0.24561403508771928</v>
+        <v>0.21768707482993196</v>
       </c>
       <c r="AA160" s="8">
-        <v>8.4936929729729727</v>
+        <v>9.1829955465587041</v>
       </c>
       <c r="AB160" s="8">
-        <v>14.052827678571429</v>
+        <v>12.660763888888889</v>
       </c>
       <c r="AC160" s="8">
         <v>21.622295999999999</v>
       </c>
       <c r="AD160" s="8">
-        <v>28.19575964912281</v>
+        <v>26.940362585034013</v>
       </c>
       <c r="AE160" s="6">
-        <v>0.57894736842105265</v>
+        <v>0.59183673469387754</v>
       </c>
       <c r="AF160" s="9"/>
       <c r="AG160" s="5">
-        <v>-640.39999999999998</v>
+        <v>-827.79999999999995</v>
       </c>
       <c r="AH160" s="10">
         <v>2</v>
@@ -21754,7 +21748,7 @@
         <v>42127.150000000001</v>
       </c>
       <c r="Q161" s="6">
-        <v>-0.036694520495007432</v>
+        <v>-0.13202140815308105</v>
       </c>
       <c r="R161" s="7">
         <v>465</v>
@@ -21790,7 +21784,7 @@
         <v>7.3828253048780486</v>
       </c>
       <c r="AC161" s="8">
-        <v>14.038346000000001</v>
+        <v>14.070425</v>
       </c>
       <c r="AD161" s="8">
         <v>20.867426747720362</v>
@@ -21885,7 +21879,7 @@
         <v>23996.599999999999</v>
       </c>
       <c r="Q162" s="6">
-        <v>0.080654356870017541</v>
+        <v>-0.015873341357836357</v>
       </c>
       <c r="R162" s="7">
         <v>319</v>
@@ -21921,7 +21915,7 @@
         <v>14.326134090909092</v>
       </c>
       <c r="AC162" s="8">
-        <v>29.767530000000001</v>
+        <v>24.979469000000002</v>
       </c>
       <c r="AD162" s="8">
         <v>29.816334000000001</v>
@@ -22016,7 +22010,7 @@
         <v>71054.050000000003</v>
       </c>
       <c r="Q163" s="6">
-        <v>0.26789539932770579</v>
+        <v>0.12553453903077449</v>
       </c>
       <c r="R163" s="7">
         <v>710</v>
@@ -22052,7 +22046,7 @@
         <v>5.6620418848167544</v>
       </c>
       <c r="AC163" s="8">
-        <v>9.3278619999999997</v>
+        <v>8.8954719999999998</v>
       </c>
       <c r="AD163" s="8">
         <v>14.358078352941176</v>
@@ -22147,7 +22141,7 @@
         <v>15063.51</v>
       </c>
       <c r="Q164" s="6">
-        <v>0.059595759228152634</v>
+        <v>-0.019803681061436595</v>
       </c>
       <c r="R164" s="7">
         <v>255</v>
@@ -22183,7 +22177,7 @@
         <v>6.0572912500000005</v>
       </c>
       <c r="AC164" s="8">
-        <v>18.951180999999998</v>
+        <v>21.446885999999999</v>
       </c>
       <c r="AD164" s="8">
         <v>27.652119653179192</v>
@@ -22235,7 +22229,7 @@
         <v>19951</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>44</v>
@@ -22272,59 +22266,59 @@
         <v>52</v>
       </c>
       <c r="O165" s="5">
-        <v>25290.59</v>
+        <v>35190.650000000001</v>
       </c>
       <c r="P165" s="5">
-        <v>29505.688333333335</v>
+        <v>35190.650000000001</v>
       </c>
       <c r="Q165" s="6">
-        <v>-0.26762430528734538</v>
+        <v>-0.21690749821142663</v>
       </c>
       <c r="R165" s="7">
-        <v>298.66666666666663</v>
+        <v>358</v>
       </c>
       <c r="S165" s="6">
-        <v>-0.36159600997506236</v>
+        <v>-0.32833020637898691</v>
       </c>
       <c r="T165" s="6">
-        <v>0.37933108717511138</v>
+        <v>0.37409972535318331</v>
       </c>
       <c r="U165" s="6">
-        <v>0.020439499434374606</v>
+        <v>0.01614867869732443</v>
       </c>
       <c r="V165" s="6">
-        <v>0.031101567816330104</v>
+        <v>0.025434639598870722</v>
       </c>
       <c r="W165" s="6">
-        <v>-0.0051071564562155339</v>
+        <v>-0.004337188997645681</v>
       </c>
       <c r="X165" s="8">
-        <v>25.397344202898552</v>
+        <v>25.279775000000001</v>
       </c>
       <c r="Y165" s="6">
-        <v>0.44927536231884058</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="Z165" s="6">
-        <v>0.065217391304347824</v>
+        <v>0.057291666666666664</v>
       </c>
       <c r="AA165" s="8">
-        <v>4.6653440476190475</v>
+        <v>5.3391573863636363</v>
       </c>
       <c r="AB165" s="8">
-        <v>5.0143374999999999</v>
+        <v>4.5439148148148147</v>
       </c>
       <c r="AC165" s="8">
-        <v>10.293758</v>
+        <v>10.046704999999999</v>
       </c>
       <c r="AD165" s="8">
-        <v>16.871739130434783</v>
+        <v>16.864930729166666</v>
       </c>
       <c r="AE165" s="6">
-        <v>0.75362318840579712</v>
+        <v>0.765625</v>
       </c>
       <c r="AF165" s="9"/>
       <c r="AG165" s="5">
-        <v>-1305.1300000000001</v>
+        <v>-1694.3599999999999</v>
       </c>
       <c r="AH165" s="10">
         <v>1</v>
@@ -22366,7 +22360,7 @@
         <v>19954</v>
       </c>
       <c r="B166" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C166" s="4">
         <v>44</v>
@@ -22403,59 +22397,59 @@
         <v>52</v>
       </c>
       <c r="O166" s="5">
-        <v>10493.83</v>
+        <v>14469.01</v>
       </c>
       <c r="P166" s="5">
-        <v>12242.801666666666</v>
+        <v>14469.01</v>
       </c>
       <c r="Q166" s="6">
-        <v>-0.11537574078155244</v>
+        <v>-0.031255042404740752</v>
       </c>
       <c r="R166" s="7">
-        <v>157.5</v>
+        <v>184</v>
       </c>
       <c r="S166" s="6">
-        <v>-0.34782608695652173</v>
+        <v>-0.26400000000000001</v>
       </c>
       <c r="T166" s="6">
-        <v>0.41077435026105819</v>
+        <v>0.53399996959017926</v>
       </c>
       <c r="U166" s="6">
-        <v>0.054339187884690332</v>
+        <v>0.16814218111674537</v>
       </c>
       <c r="V166" s="6">
-        <v>0.13131787917280915</v>
+        <v>0.11871648440356321</v>
       </c>
       <c r="W166" s="6">
-        <v>0.062031450862078001</v>
+        <v>0.060982057514646824</v>
       </c>
       <c r="X166" s="8">
-        <v>24.459187179487181</v>
+        <v>25.084751063829788</v>
       </c>
       <c r="Y166" s="6">
-        <v>0.82051282051282048</v>
+        <v>0.82978723404255317</v>
       </c>
       <c r="Z166" s="6">
-        <v>0.038461538461538464</v>
+        <v>0.031914893617021274</v>
       </c>
       <c r="AA166" s="8">
-        <v>5.9176765151515145</v>
+        <v>7.2062613259668513</v>
       </c>
       <c r="AB166" s="8">
-        <v>2.6974358974358976</v>
+        <v>2.6549648936170214</v>
       </c>
       <c r="AC166" s="8">
-        <v>8.7791329999999999</v>
+        <v>9.1449029999999993</v>
       </c>
       <c r="AD166" s="8">
-        <v>16.157906410256412</v>
+        <v>16.706206382978724</v>
       </c>
       <c r="AE166" s="6">
-        <v>0.82051282051282048</v>
+        <v>0.7978723404255319</v>
       </c>
       <c r="AF166" s="9"/>
       <c r="AG166" s="5">
-        <v>-443.79000000000002</v>
+        <v>-756.78999999999996</v>
       </c>
       <c r="AH166" s="10">
         <v>3</v>
@@ -22497,7 +22491,7 @@
         <v>19956</v>
       </c>
       <c r="B167" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C167" s="4">
         <v>44</v>
@@ -22534,59 +22528,59 @@
         <v>52</v>
       </c>
       <c r="O167" s="5">
-        <v>8319.8400000000001</v>
+        <v>11068.309999999999</v>
       </c>
       <c r="P167" s="5">
-        <v>9706.4800000000014</v>
+        <v>11068.309999999999</v>
       </c>
       <c r="Q167" s="6">
-        <v>-0.6653219522219509</v>
+        <v>-0.63363165852831838</v>
       </c>
       <c r="R167" s="7">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="S167" s="6">
-        <v>-0.63139931740614341</v>
+        <v>-0.61325966850828728</v>
       </c>
       <c r="T167" s="6">
-        <v>0.33999242773899496</v>
+        <v>0.3338303950648292</v>
       </c>
       <c r="U167" s="6">
-        <v>-0.03561215119521529</v>
+        <v>-0.034209531536431491</v>
       </c>
       <c r="V167" s="6">
-        <v>0.067962845439335381</v>
+        <v>0.071340294950177574</v>
       </c>
       <c r="W167" s="6">
-        <v>0.036248293236408387</v>
+        <v>0.044140117145255245</v>
       </c>
       <c r="X167" s="8">
-        <v>29.637379999999997</v>
+        <v>31.654760714285711</v>
       </c>
       <c r="Y167" s="6">
-        <v>0.81690140845070425</v>
+        <v>0.82352941176470584</v>
       </c>
       <c r="Z167" s="6">
-        <v>0.11428571428571428</v>
+        <v>0.17857142857142858</v>
       </c>
       <c r="AA167" s="8">
-        <v>6.5726086956521739</v>
+        <v>6.7416669014084505</v>
       </c>
       <c r="AB167" s="8">
-        <v>10.455475714285713</v>
+        <v>11.047816666666668</v>
       </c>
       <c r="AC167" s="8">
         <v>16.542525999999999</v>
       </c>
       <c r="AD167" s="8">
-        <v>23.389284285714286</v>
+        <v>24.258927380952382</v>
       </c>
       <c r="AE167" s="6">
-        <v>0.59999999999999998</v>
+        <v>0.5</v>
       </c>
       <c r="AF167" s="9"/>
       <c r="AG167" s="5">
-        <v>-885.97000000000003</v>
+        <v>-2680.2399999999998</v>
       </c>
       <c r="AH167" s="10">
         <v>4</v>
@@ -22671,7 +22665,7 @@
         <v>29813.259999999998</v>
       </c>
       <c r="Q168" s="6">
-        <v>-0.28874507889748213</v>
+        <v>-0.3298472416597471</v>
       </c>
       <c r="R168" s="7">
         <v>327</v>
@@ -22680,10 +22674,10 @@
         <v>-0.39219330855018586</v>
       </c>
       <c r="T168" s="6">
-        <v>0.38950464659014145</v>
+        <v>0.38780060617322631</v>
       </c>
       <c r="U168" s="6">
-        <v>0.049730666824091024</v>
+        <v>0.048026626407175872</v>
       </c>
       <c r="V168" s="6">
         <v>0.028156816798967976</v>
@@ -22707,7 +22701,7 @@
         <v>7.1966911764705879</v>
       </c>
       <c r="AC168" s="8">
-        <v>16.676556000000001</v>
+        <v>17.146211000000001</v>
       </c>
       <c r="AD168" s="8">
         <v>23.897810218978101</v>
@@ -22834,7 +22828,7 @@
         <v>3.5294028301886788</v>
       </c>
       <c r="AC169" s="8">
-        <v>8.9529630000000004</v>
+        <v>8.9081220000000005</v>
       </c>
       <c r="AD169" s="8">
         <v>15.849214150943395</v>
@@ -22886,7 +22880,7 @@
         <v>19961</v>
       </c>
       <c r="B170" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C170" s="4">
         <v>44</v>
@@ -22923,55 +22917,55 @@
         <v>52</v>
       </c>
       <c r="O170" s="5">
-        <v>18647.489999999998</v>
+        <v>22541.039999999997</v>
       </c>
       <c r="P170" s="5">
-        <v>21755.404999999999</v>
+        <v>22541.039999999997</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="7">
-        <v>238</v>
+        <v>246.00000000000003</v>
       </c>
       <c r="S170" s="6"/>
       <c r="T170" s="6">
-        <v>0.31326214412770831</v>
+        <v>0.32577732881890098</v>
       </c>
       <c r="U170" s="6">
-        <v>-0.040423526168937476</v>
+        <v>-0.026683338479502276</v>
       </c>
       <c r="V170" s="6">
-        <v>0.0315544344037723</v>
+        <v>0.031748091481138399</v>
       </c>
       <c r="W170" s="6">
-        <v>0.014532840612865321</v>
+        <v>0.015242641865681439</v>
       </c>
       <c r="X170" s="8">
-        <v>37.003549074074073</v>
+        <v>35.814885496183209</v>
       </c>
       <c r="Y170" s="6">
-        <v>0.34259259259259262</v>
+        <v>0.38167938931297712</v>
       </c>
       <c r="Z170" s="6">
-        <v>0.32407407407407407</v>
+        <v>0.28244274809160308</v>
       </c>
       <c r="AA170" s="8">
-        <v>7.2272572916666666</v>
+        <v>6.9891056277056283</v>
       </c>
       <c r="AB170" s="8">
-        <v>10.261793396226414</v>
+        <v>9.5944449612403098</v>
       </c>
       <c r="AC170" s="8">
-        <v>11.989853</v>
+        <v>17.92164</v>
       </c>
       <c r="AD170" s="8">
-        <v>24.595061111111111</v>
+        <v>23.610559541984731</v>
       </c>
       <c r="AE170" s="6">
-        <v>0.44444444444444442</v>
+        <v>0.4580152671755725</v>
       </c>
       <c r="AF170" s="9"/>
       <c r="AG170" s="5">
-        <v>-1001.1</v>
+        <v>-1339.0999999999999</v>
       </c>
       <c r="AH170" s="10">
         <v>2</v>
@@ -23215,7 +23209,7 @@
         <v>7.0470634361233477</v>
       </c>
       <c r="AC172" s="8">
-        <v>19.289702999999999</v>
+        <v>18.479146</v>
       </c>
       <c r="AD172" s="8">
         <v>25.402110917030569</v>
@@ -23433,7 +23427,7 @@
         <v>6.7356904040404038</v>
       </c>
       <c r="AC174" s="8">
-        <v>11.231318</v>
+        <v>13.669187000000001</v>
       </c>
       <c r="AD174" s="8">
         <v>20.329310344827586</v>
